--- a/Lesson_development/merged_dataset_ref_with_doi.xlsx
+++ b/Lesson_development/merged_dataset_ref_with_doi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/linigodelacruz_tudelft_nl/Documents/Documents/4TU.ResearchData/Projects/TRAINING/WebAPI_with_uses_cases/USES-CASES/Sync_Pure_4TU_WUR/Lesson_development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_76A953B3D350DFA180E81DD04B5ED87656C67458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{304FEF2D-9C5C-4BFF-8CED-5BCD1EDD4849}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_76A953B3D350DFA180E81DD04B5ED87656C67458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58F17F5E-68A7-4083-8D4E-5484B8052623}"/>
   <bookViews>
-    <workbookView xWindow="32025" yWindow="4245" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12873,13 +12873,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I887"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100.140625" customWidth="1"/>
     <col min="2" max="2" width="55.5703125" customWidth="1"/>
     <col min="3" max="3" width="52.5703125" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="34.7109375" customWidth="1"/>
     <col min="7" max="7" width="36.5703125" customWidth="1"/>
@@ -12916,7 +12917,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -12945,7 +12946,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -12974,7 +12975,7 @@
         <v>45197</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -13330,7 +13331,7 @@
         <v>44426</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>100</v>
       </c>
@@ -13359,7 +13360,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -13388,7 +13389,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -13417,7 +13418,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -13446,7 +13447,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>125</v>
       </c>
@@ -13611,7 +13612,7 @@
         <v>45460</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>162</v>
       </c>
@@ -13640,7 +13641,7 @@
         <v>44545</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>169</v>
       </c>
@@ -13669,7 +13670,7 @@
         <v>44502</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>176</v>
       </c>
@@ -13715,7 +13716,7 @@
         <v>43105</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>187</v>
       </c>
@@ -13744,7 +13745,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>194</v>
       </c>
@@ -13773,7 +13774,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>202</v>
       </c>
@@ -13802,7 +13803,7 @@
         <v>45238</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>209</v>
       </c>
@@ -13831,7 +13832,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>216</v>
       </c>
@@ -13860,7 +13861,7 @@
         <v>44760</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>223</v>
       </c>
@@ -13886,7 +13887,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>223</v>
       </c>
@@ -13912,7 +13913,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>223</v>
       </c>
@@ -13941,7 +13942,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>223</v>
       </c>
@@ -13987,7 +13988,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>237</v>
       </c>
@@ -14016,7 +14017,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>244</v>
       </c>
@@ -14045,7 +14046,7 @@
         <v>43269</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>250</v>
       </c>
@@ -14074,7 +14075,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>250</v>
       </c>
@@ -14103,7 +14104,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>250</v>
       </c>
@@ -14132,7 +14133,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>250</v>
       </c>
@@ -14161,7 +14162,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>250</v>
       </c>
@@ -14190,7 +14191,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>250</v>
       </c>
@@ -14219,7 +14220,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>250</v>
       </c>
@@ -14248,7 +14249,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>250</v>
       </c>
@@ -14277,7 +14278,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>250</v>
       </c>
@@ -14306,7 +14307,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>250</v>
       </c>
@@ -14335,7 +14336,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>250</v>
       </c>
@@ -14364,7 +14365,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>250</v>
       </c>
@@ -14393,7 +14394,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>250</v>
       </c>
@@ -14422,7 +14423,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>250</v>
       </c>
@@ -14451,7 +14452,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>250</v>
       </c>
@@ -14480,7 +14481,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>250</v>
       </c>
@@ -14509,7 +14510,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>250</v>
       </c>
@@ -14538,7 +14539,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>250</v>
       </c>
@@ -14567,7 +14568,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>250</v>
       </c>
@@ -14596,7 +14597,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>250</v>
       </c>
@@ -14625,7 +14626,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>250</v>
       </c>
@@ -14654,7 +14655,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>250</v>
       </c>
@@ -14683,7 +14684,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>250</v>
       </c>
@@ -14712,7 +14713,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>250</v>
       </c>
@@ -14741,7 +14742,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>250</v>
       </c>
@@ -14804,7 +14805,7 @@
         <v>44063</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>279</v>
       </c>
@@ -14833,7 +14834,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>279</v>
       </c>
@@ -14862,7 +14863,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>279</v>
       </c>
@@ -14891,7 +14892,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>279</v>
       </c>
@@ -14920,7 +14921,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>289</v>
       </c>
@@ -14949,7 +14950,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>296</v>
       </c>
@@ -14978,7 +14979,7 @@
         <v>42831</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>303</v>
       </c>
@@ -15007,7 +15008,7 @@
         <v>44300</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>303</v>
       </c>
@@ -15036,7 +15037,7 @@
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>303</v>
       </c>
@@ -15062,7 +15063,7 @@
         <v>44300</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>303</v>
       </c>
@@ -15088,7 +15089,7 @@
         <v>44300</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>312</v>
       </c>
@@ -15117,7 +15118,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>316</v>
       </c>
@@ -15146,7 +15147,7 @@
         <v>43993</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>323</v>
       </c>
@@ -15192,7 +15193,7 @@
         <v>44615</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>334</v>
       </c>
@@ -15221,7 +15222,7 @@
         <v>42678</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>341</v>
       </c>
@@ -15284,7 +15285,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>359</v>
       </c>
@@ -15313,7 +15314,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>359</v>
       </c>
@@ -15342,7 +15343,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>359</v>
       </c>
@@ -15371,7 +15372,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>359</v>
       </c>
@@ -15400,7 +15401,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>359</v>
       </c>
@@ -15429,7 +15430,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>359</v>
       </c>
@@ -15458,7 +15459,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>359</v>
       </c>
@@ -15487,7 +15488,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>359</v>
       </c>
@@ -15516,7 +15517,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>359</v>
       </c>
@@ -15545,7 +15546,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>359</v>
       </c>
@@ -15571,7 +15572,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>359</v>
       </c>
@@ -15597,7 +15598,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>359</v>
       </c>
@@ -15626,7 +15627,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>359</v>
       </c>
@@ -15655,7 +15656,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>359</v>
       </c>
@@ -15684,7 +15685,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>359</v>
       </c>
@@ -15713,7 +15714,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>359</v>
       </c>
@@ -15742,7 +15743,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>359</v>
       </c>
@@ -15771,7 +15772,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>359</v>
       </c>
@@ -15797,7 +15798,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>359</v>
       </c>
@@ -15823,7 +15824,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>359</v>
       </c>
@@ -15852,7 +15853,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>359</v>
       </c>
@@ -15881,7 +15882,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>359</v>
       </c>
@@ -15910,7 +15911,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>359</v>
       </c>
@@ -15939,7 +15940,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>359</v>
       </c>
@@ -15968,7 +15969,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>359</v>
       </c>
@@ -15997,7 +15998,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>359</v>
       </c>
@@ -16026,7 +16027,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>359</v>
       </c>
@@ -16055,7 +16056,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>359</v>
       </c>
@@ -16084,7 +16085,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>359</v>
       </c>
@@ -16113,7 +16114,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>359</v>
       </c>
@@ -16142,7 +16143,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>359</v>
       </c>
@@ -16171,7 +16172,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>359</v>
       </c>
@@ -16200,7 +16201,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>359</v>
       </c>
@@ -16229,7 +16230,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>359</v>
       </c>
@@ -16258,7 +16259,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>359</v>
       </c>
@@ -16287,7 +16288,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>359</v>
       </c>
@@ -16316,7 +16317,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>359</v>
       </c>
@@ -16345,7 +16346,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>359</v>
       </c>
@@ -16374,7 +16375,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>359</v>
       </c>
@@ -16403,7 +16404,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>359</v>
       </c>
@@ -16432,7 +16433,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>359</v>
       </c>
@@ -16461,7 +16462,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>359</v>
       </c>
@@ -16490,7 +16491,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>359</v>
       </c>
@@ -16519,7 +16520,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>359</v>
       </c>
@@ -16548,7 +16549,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>359</v>
       </c>
@@ -16577,7 +16578,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>359</v>
       </c>
@@ -16606,7 +16607,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>359</v>
       </c>
@@ -16635,7 +16636,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>359</v>
       </c>
@@ -16664,7 +16665,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>359</v>
       </c>
@@ -16693,7 +16694,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>359</v>
       </c>
@@ -16722,7 +16723,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>359</v>
       </c>
@@ -16751,7 +16752,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>359</v>
       </c>
@@ -16780,7 +16781,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>359</v>
       </c>
@@ -16809,7 +16810,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>359</v>
       </c>
@@ -16838,7 +16839,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>359</v>
       </c>
@@ -16867,7 +16868,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>359</v>
       </c>
@@ -16896,7 +16897,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>359</v>
       </c>
@@ -16925,7 +16926,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>359</v>
       </c>
@@ -16954,7 +16955,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>359</v>
       </c>
@@ -16983,7 +16984,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>359</v>
       </c>
@@ -17012,7 +17013,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>359</v>
       </c>
@@ -17041,7 +17042,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>359</v>
       </c>
@@ -17070,7 +17071,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>359</v>
       </c>
@@ -17099,7 +17100,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>359</v>
       </c>
@@ -17128,7 +17129,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>385</v>
       </c>
@@ -17174,7 +17175,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>396</v>
       </c>
@@ -17203,7 +17204,7 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>403</v>
       </c>
@@ -17283,7 +17284,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>425</v>
       </c>
@@ -17312,7 +17313,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>432</v>
       </c>
@@ -17341,7 +17342,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>440</v>
       </c>
@@ -17370,7 +17371,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>447</v>
       </c>
@@ -17399,7 +17400,7 @@
         <v>44350</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>454</v>
       </c>
@@ -17428,7 +17429,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>462</v>
       </c>
@@ -17457,7 +17458,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>470</v>
       </c>
@@ -17503,7 +17504,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>482</v>
       </c>
@@ -17549,7 +17550,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>493</v>
       </c>
@@ -17595,7 +17596,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>504</v>
       </c>
@@ -17624,7 +17625,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>512</v>
       </c>
@@ -17653,7 +17654,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>519</v>
       </c>
@@ -17682,7 +17683,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>527</v>
       </c>
@@ -17728,7 +17729,7 @@
         <v>45315</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>538</v>
       </c>
@@ -17757,7 +17758,7 @@
         <v>45902</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>545</v>
       </c>
@@ -17803,7 +17804,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>557</v>
       </c>
@@ -17866,7 +17867,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>572</v>
       </c>
@@ -17912,7 +17913,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>585</v>
       </c>
@@ -17958,7 +17959,7 @@
         <v>45477</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>596</v>
       </c>
@@ -18004,7 +18005,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>608</v>
       </c>
@@ -18033,7 +18034,7 @@
         <v>43797</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>615</v>
       </c>
@@ -18062,7 +18063,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>622</v>
       </c>
@@ -18091,7 +18092,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>630</v>
       </c>
@@ -18120,7 +18121,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>636</v>
       </c>
@@ -18149,7 +18150,7 @@
         <v>44564</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>643</v>
       </c>
@@ -18178,7 +18179,7 @@
         <v>44551</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>650</v>
       </c>
@@ -18207,7 +18208,7 @@
         <v>44551</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>657</v>
       </c>
@@ -18253,7 +18254,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>668</v>
       </c>
@@ -18299,7 +18300,7 @@
         <v>44516</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>680</v>
       </c>
@@ -18328,7 +18329,7 @@
         <v>44363</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>687</v>
       </c>
@@ -18357,7 +18358,7 @@
         <v>44183</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>694</v>
       </c>
@@ -18386,7 +18387,7 @@
         <v>44516</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>701</v>
       </c>
@@ -18415,7 +18416,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>709</v>
       </c>
@@ -18444,7 +18445,7 @@
         <v>43860</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>716</v>
       </c>
@@ -18473,7 +18474,7 @@
         <v>43860</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>720</v>
       </c>
@@ -18502,7 +18503,7 @@
         <v>43860</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>724</v>
       </c>
@@ -18531,7 +18532,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>728</v>
       </c>
@@ -18560,7 +18561,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>732</v>
       </c>
@@ -18606,7 +18607,7 @@
         <v>42736</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>743</v>
       </c>
@@ -18635,7 +18636,7 @@
         <v>44655</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>750</v>
       </c>
@@ -18664,7 +18665,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>757</v>
       </c>
@@ -18704,7 +18705,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>769</v>
       </c>
@@ -18733,7 +18734,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>777</v>
       </c>
@@ -18762,7 +18763,7 @@
         <v>45273</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>784</v>
       </c>
@@ -18808,7 +18809,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>795</v>
       </c>
@@ -18837,7 +18838,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>803</v>
       </c>
@@ -18877,7 +18878,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>811</v>
       </c>
@@ -18906,7 +18907,7 @@
         <v>43580</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>818</v>
       </c>
@@ -18952,7 +18953,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>829</v>
       </c>
@@ -18981,7 +18982,7 @@
         <v>44607</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>836</v>
       </c>
@@ -19010,7 +19011,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>844</v>
       </c>
@@ -19039,7 +19040,7 @@
         <v>45321</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>844</v>
       </c>
@@ -19102,7 +19103,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>860</v>
       </c>
@@ -19131,7 +19132,7 @@
         <v>44355</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>867</v>
       </c>
@@ -19160,7 +19161,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>867</v>
       </c>
@@ -19189,7 +19190,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>867</v>
       </c>
@@ -19218,7 +19219,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>867</v>
       </c>
@@ -19247,7 +19248,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>875</v>
       </c>
@@ -19276,7 +19277,7 @@
         <v>44147</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>882</v>
       </c>
@@ -19305,7 +19306,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>889</v>
       </c>
@@ -19334,7 +19335,7 @@
         <v>43370</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>896</v>
       </c>
@@ -19380,7 +19381,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>907</v>
       </c>
@@ -19409,7 +19410,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>907</v>
       </c>
@@ -19438,7 +19439,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>907</v>
       </c>
@@ -19467,7 +19468,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>907</v>
       </c>
@@ -19496,7 +19497,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>917</v>
       </c>
@@ -19525,7 +19526,7 @@
         <v>43356</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>924</v>
       </c>
@@ -19571,7 +19572,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>935</v>
       </c>
@@ -19600,7 +19601,7 @@
         <v>43580</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>942</v>
       </c>
@@ -19629,7 +19630,7 @@
         <v>45028</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>949</v>
       </c>
@@ -19658,7 +19659,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>949</v>
       </c>
@@ -19687,7 +19688,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>949</v>
       </c>
@@ -19716,7 +19717,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>949</v>
       </c>
@@ -19745,7 +19746,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>959</v>
       </c>
@@ -19774,7 +19775,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>963</v>
       </c>
@@ -19803,7 +19804,7 @@
         <v>43811</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>970</v>
       </c>
@@ -19832,7 +19833,7 @@
         <v>43368</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>977</v>
       </c>
@@ -19878,7 +19879,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>989</v>
       </c>
@@ -19918,7 +19919,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1001</v>
       </c>
@@ -19947,7 +19948,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1006</v>
       </c>
@@ -20010,7 +20011,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1022</v>
       </c>
@@ -20039,7 +20040,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1022</v>
       </c>
@@ -20068,7 +20069,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1022</v>
       </c>
@@ -20097,7 +20098,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1022</v>
       </c>
@@ -20126,7 +20127,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1022</v>
       </c>
@@ -20155,7 +20156,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1022</v>
       </c>
@@ -20184,7 +20185,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1022</v>
       </c>
@@ -20213,7 +20214,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1022</v>
       </c>
@@ -20242,7 +20243,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1022</v>
       </c>
@@ -20271,7 +20272,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1035</v>
       </c>
@@ -20300,7 +20301,7 @@
         <v>43858</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1042</v>
       </c>
@@ -20329,7 +20330,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1049</v>
       </c>
@@ -20358,7 +20359,7 @@
         <v>43935</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1056</v>
       </c>
@@ -20387,7 +20388,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1064</v>
       </c>
@@ -20416,7 +20417,7 @@
         <v>43846</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1071</v>
       </c>
@@ -20445,7 +20446,7 @@
         <v>45167</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1078</v>
       </c>
@@ -20474,7 +20475,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1085</v>
       </c>
@@ -20503,7 +20504,7 @@
         <v>43668</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1092</v>
       </c>
@@ -20532,7 +20533,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1099</v>
       </c>
@@ -20561,7 +20562,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1099</v>
       </c>
@@ -20590,7 +20591,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1099</v>
       </c>
@@ -20619,7 +20620,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1099</v>
       </c>
@@ -20665,7 +20666,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1114</v>
       </c>
@@ -20694,7 +20695,7 @@
         <v>43522</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1120</v>
       </c>
@@ -20723,7 +20724,7 @@
         <v>44404</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1127</v>
       </c>
@@ -20752,7 +20753,7 @@
         <v>44417</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1134</v>
       </c>
@@ -20781,7 +20782,7 @@
         <v>45329</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1141</v>
       </c>
@@ -20810,7 +20811,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1149</v>
       </c>
@@ -20839,7 +20840,7 @@
         <v>44867</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1156</v>
       </c>
@@ -20868,7 +20869,7 @@
         <v>44942</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1163</v>
       </c>
@@ -20897,7 +20898,7 @@
         <v>44599</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1170</v>
       </c>
@@ -20926,7 +20927,7 @@
         <v>44819</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1177</v>
       </c>
@@ -20955,7 +20956,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1185</v>
       </c>
@@ -20984,7 +20985,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1193</v>
       </c>
@@ -21013,7 +21014,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1200</v>
       </c>
@@ -21059,7 +21060,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1212</v>
       </c>
@@ -21088,7 +21089,7 @@
         <v>45538</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1219</v>
       </c>
@@ -21134,7 +21135,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1231</v>
       </c>
@@ -21163,7 +21164,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1238</v>
       </c>
@@ -21209,7 +21210,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1249</v>
       </c>
@@ -21272,7 +21273,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1265</v>
       </c>
@@ -21318,7 +21319,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1278</v>
       </c>
@@ -21347,7 +21348,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1286</v>
       </c>
@@ -21393,7 +21394,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1298</v>
       </c>
@@ -21436,7 +21437,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1310</v>
       </c>
@@ -21465,7 +21466,7 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1317</v>
       </c>
@@ -21511,7 +21512,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1328</v>
       </c>
@@ -21557,7 +21558,7 @@
         <v>45904</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1340</v>
       </c>
@@ -21603,7 +21604,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1351</v>
       </c>
@@ -21632,7 +21633,7 @@
         <v>45168</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1358</v>
       </c>
@@ -21661,7 +21662,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1365</v>
       </c>
@@ -21690,7 +21691,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1372</v>
       </c>
@@ -21736,7 +21737,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1383</v>
       </c>
@@ -21782,7 +21783,7 @@
         <v>45406</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1394</v>
       </c>
@@ -21828,7 +21829,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1406</v>
       </c>
@@ -21857,7 +21858,7 @@
         <v>45327</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1413</v>
       </c>
@@ -21886,7 +21887,7 @@
         <v>45327</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1420</v>
       </c>
@@ -21915,7 +21916,7 @@
         <v>45327</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1427</v>
       </c>
@@ -21944,7 +21945,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1435</v>
       </c>
@@ -21973,7 +21974,7 @@
         <v>44461</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1442</v>
       </c>
@@ -22002,7 +22003,7 @@
         <v>44442</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1449</v>
       </c>
@@ -22031,7 +22032,7 @@
         <v>44732</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1456</v>
       </c>
@@ -22060,7 +22061,7 @@
         <v>44139</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1463</v>
       </c>
@@ -22089,7 +22090,7 @@
         <v>44363</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1470</v>
       </c>
@@ -22118,7 +22119,7 @@
         <v>44405</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1477</v>
       </c>
@@ -22147,7 +22148,7 @@
         <v>44881</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1484</v>
       </c>
@@ -22176,7 +22177,7 @@
         <v>44721</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1490</v>
       </c>
@@ -22205,7 +22206,7 @@
         <v>45331</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1497</v>
       </c>
@@ -22234,7 +22235,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1504</v>
       </c>
@@ -22263,7 +22264,7 @@
         <v>45139</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1511</v>
       </c>
@@ -22292,7 +22293,7 @@
         <v>44746</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1518</v>
       </c>
@@ -22321,7 +22322,7 @@
         <v>45405</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1525</v>
       </c>
@@ -22367,7 +22368,7 @@
         <v>44379</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1536</v>
       </c>
@@ -22396,7 +22397,7 @@
         <v>45236</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1543</v>
       </c>
@@ -22425,7 +22426,7 @@
         <v>44250</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1550</v>
       </c>
@@ -22465,7 +22466,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1562</v>
       </c>
@@ -22494,7 +22495,7 @@
         <v>44231</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1565</v>
       </c>
@@ -22523,7 +22524,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1572</v>
       </c>
@@ -22552,7 +22553,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1579</v>
       </c>
@@ -22581,7 +22582,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1587</v>
       </c>
@@ -22610,7 +22611,7 @@
         <v>45085</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1594</v>
       </c>
@@ -22639,7 +22640,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1601</v>
       </c>
@@ -22668,7 +22669,7 @@
         <v>45141</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1608</v>
       </c>
@@ -22697,7 +22698,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1616</v>
       </c>
@@ -22726,7 +22727,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1623</v>
       </c>
@@ -22755,7 +22756,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1631</v>
       </c>
@@ -22784,7 +22785,7 @@
         <v>44798</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1638</v>
       </c>
@@ -22830,7 +22831,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1650</v>
       </c>
@@ -22859,7 +22860,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1658</v>
       </c>
@@ -22888,7 +22889,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1666</v>
       </c>
@@ -22917,7 +22918,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1673</v>
       </c>
@@ -22946,7 +22947,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1681</v>
       </c>
@@ -22975,7 +22976,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1688</v>
       </c>
@@ -23004,7 +23005,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1696</v>
       </c>
@@ -23033,7 +23034,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1696</v>
       </c>
@@ -23062,7 +23063,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1696</v>
       </c>
@@ -23091,7 +23092,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1696</v>
       </c>
@@ -23120,7 +23121,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1706</v>
       </c>
@@ -23149,7 +23150,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1714</v>
       </c>
@@ -23178,7 +23179,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1721</v>
       </c>
@@ -23207,7 +23208,7 @@
         <v>45282</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1728</v>
       </c>
@@ -23236,7 +23237,7 @@
         <v>44305</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1735</v>
       </c>
@@ -23265,7 +23266,7 @@
         <v>44572</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1742</v>
       </c>
@@ -23294,7 +23295,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1749</v>
       </c>
@@ -23340,7 +23341,7 @@
         <v>45861</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1760</v>
       </c>
@@ -23386,7 +23387,7 @@
         <v>45274</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1771</v>
       </c>
@@ -23432,7 +23433,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1783</v>
       </c>
@@ -23478,7 +23479,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1795</v>
       </c>
@@ -23541,7 +23542,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1811</v>
       </c>
@@ -23570,7 +23571,7 @@
         <v>45993</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1818</v>
       </c>
@@ -23599,7 +23600,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1825</v>
       </c>
@@ -23628,7 +23629,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1832</v>
       </c>
@@ -23657,7 +23658,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1840</v>
       </c>
@@ -23686,7 +23687,7 @@
         <v>44910</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1847</v>
       </c>
@@ -23732,7 +23733,7 @@
         <v>45847</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1858</v>
       </c>
@@ -23761,7 +23762,7 @@
         <v>45490</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1865</v>
       </c>
@@ -23790,7 +23791,7 @@
         <v>45503</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1872</v>
       </c>
@@ -23819,7 +23820,7 @@
         <v>44579</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1872</v>
       </c>
@@ -23848,7 +23849,7 @@
         <v>44579</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1880</v>
       </c>
@@ -23877,7 +23878,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1880</v>
       </c>
@@ -23906,7 +23907,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1880</v>
       </c>
@@ -23935,7 +23936,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1880</v>
       </c>
@@ -23992,7 +23993,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1897</v>
       </c>
@@ -24055,7 +24056,7 @@
         <v>45868</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1912</v>
       </c>
@@ -24084,7 +24085,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1919</v>
       </c>
@@ -24113,7 +24114,7 @@
         <v>45912</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1926</v>
       </c>
@@ -24142,7 +24143,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1934</v>
       </c>
@@ -24188,7 +24189,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1945</v>
       </c>
@@ -24217,7 +24218,7 @@
         <v>45896</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1952</v>
       </c>
@@ -24246,7 +24247,7 @@
         <v>44368</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1959</v>
       </c>
@@ -24326,7 +24327,7 @@
         <v>45994</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1978</v>
       </c>
@@ -24355,7 +24356,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1986</v>
       </c>
@@ -24384,7 +24385,7 @@
         <v>45237</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1986</v>
       </c>
@@ -24413,7 +24414,7 @@
         <v>45237</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1986</v>
       </c>
@@ -24442,7 +24443,7 @@
         <v>45237</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1986</v>
       </c>
@@ -24471,7 +24472,7 @@
         <v>45237</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1996</v>
       </c>
@@ -24500,7 +24501,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>2004</v>
       </c>
@@ -24529,7 +24530,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>2012</v>
       </c>
@@ -24558,7 +24559,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>2012</v>
       </c>
@@ -24587,7 +24588,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>2012</v>
       </c>
@@ -24616,7 +24617,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>2012</v>
       </c>
@@ -24645,7 +24646,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>2021</v>
       </c>
@@ -24674,7 +24675,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>2028</v>
       </c>
@@ -24720,7 +24721,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>2040</v>
       </c>
@@ -24749,7 +24750,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>2047</v>
       </c>
@@ -24778,7 +24779,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>2054</v>
       </c>
@@ -24807,7 +24808,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>2062</v>
       </c>
@@ -24853,7 +24854,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>2074</v>
       </c>
@@ -24882,7 +24883,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>2081</v>
       </c>
@@ -24911,7 +24912,7 @@
         <v>44575</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>2088</v>
       </c>
@@ -24957,7 +24958,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>2099</v>
       </c>
@@ -24986,7 +24987,7 @@
         <v>45247</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>2106</v>
       </c>
@@ -25015,7 +25016,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>2113</v>
       </c>
@@ -25044,7 +25045,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>2120</v>
       </c>
@@ -25073,7 +25074,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>2127</v>
       </c>
@@ -25102,7 +25103,7 @@
         <v>44186</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>2134</v>
       </c>
@@ -25131,7 +25132,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>2141</v>
       </c>
@@ -25177,7 +25178,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>2153</v>
       </c>
@@ -25206,7 +25207,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>2161</v>
       </c>
@@ -25269,7 +25270,7 @@
         <v>44931</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>2173</v>
       </c>
@@ -25298,7 +25299,7 @@
         <v>43998</v>
       </c>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>2180</v>
       </c>
@@ -25327,7 +25328,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>2187</v>
       </c>
@@ -25356,7 +25357,7 @@
         <v>44825</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>2194</v>
       </c>
@@ -25385,7 +25386,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>2202</v>
       </c>
@@ -25414,7 +25415,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>2209</v>
       </c>
@@ -25443,7 +25444,7 @@
         <v>44963</v>
       </c>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>2216</v>
       </c>
@@ -25472,7 +25473,7 @@
         <v>44572</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>2223</v>
       </c>
@@ -25501,7 +25502,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>2223</v>
       </c>
@@ -25530,7 +25531,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>2223</v>
       </c>
@@ -25559,7 +25560,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>2223</v>
       </c>
@@ -25599,7 +25600,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>2235</v>
       </c>
@@ -25628,7 +25629,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>2242</v>
       </c>
@@ -25674,7 +25675,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>2254</v>
       </c>
@@ -25703,7 +25704,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>2261</v>
       </c>
@@ -25732,7 +25733,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>2269</v>
       </c>
@@ -25778,7 +25779,7 @@
         <v>45518</v>
       </c>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>2280</v>
       </c>
@@ -25841,7 +25842,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>2296</v>
       </c>
@@ -25870,7 +25871,7 @@
         <v>44796</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>2303</v>
       </c>
@@ -25916,7 +25917,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>2314</v>
       </c>
@@ -25945,7 +25946,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>2319</v>
       </c>
@@ -26008,7 +26009,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>2335</v>
       </c>
@@ -26037,7 +26038,7 @@
         <v>45092</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>2342</v>
       </c>
@@ -26066,7 +26067,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>2349</v>
       </c>
@@ -26095,7 +26096,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>2356</v>
       </c>
@@ -26124,7 +26125,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>2356</v>
       </c>
@@ -26153,7 +26154,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>2356</v>
       </c>
@@ -26182,7 +26183,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>2356</v>
       </c>
@@ -26211,7 +26212,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>2366</v>
       </c>
@@ -26240,7 +26241,7 @@
         <v>45536</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>2373</v>
       </c>
@@ -26303,7 +26304,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>2388</v>
       </c>
@@ -26332,7 +26333,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>2395</v>
       </c>
@@ -26361,7 +26362,7 @@
         <v>44029</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>2402</v>
       </c>
@@ -26390,7 +26391,7 @@
         <v>46015</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>2409</v>
       </c>
@@ -26419,7 +26420,7 @@
         <v>2416</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>2417</v>
       </c>
@@ -26448,7 +26449,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>2425</v>
       </c>
@@ -26477,7 +26478,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>2432</v>
       </c>
@@ -26506,7 +26507,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>2439</v>
       </c>
@@ -26535,7 +26536,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>2439</v>
       </c>
@@ -26564,7 +26565,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>2439</v>
       </c>
@@ -26593,7 +26594,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>2439</v>
       </c>
@@ -26622,7 +26623,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>2449</v>
       </c>
@@ -26662,7 +26663,7 @@
         <v>2456</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>2457</v>
       </c>
@@ -26691,7 +26692,7 @@
         <v>44830</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>2464</v>
       </c>
@@ -26737,7 +26738,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>2475</v>
       </c>
@@ -26783,7 +26784,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>2486</v>
       </c>
@@ -26812,7 +26813,7 @@
         <v>44203</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>2493</v>
       </c>
@@ -26858,7 +26859,7 @@
         <v>45842</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>2504</v>
       </c>
@@ -26887,7 +26888,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>2512</v>
       </c>
@@ -26916,7 +26917,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>2519</v>
       </c>
@@ -26962,7 +26963,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>2531</v>
       </c>
@@ -27008,7 +27009,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>2542</v>
       </c>
@@ -27037,7 +27038,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>2550</v>
       </c>
@@ -27066,7 +27067,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>2554</v>
       </c>
@@ -27095,7 +27096,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>2558</v>
       </c>
@@ -27158,7 +27159,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>2573</v>
       </c>
@@ -27187,7 +27188,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>2580</v>
       </c>
@@ -27216,7 +27217,7 @@
         <v>45240</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>2587</v>
       </c>
@@ -27245,7 +27246,7 @@
         <v>44557</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>2594</v>
       </c>
@@ -27274,7 +27275,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>2601</v>
       </c>
@@ -27320,7 +27321,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>2612</v>
       </c>
@@ -27349,7 +27350,7 @@
         <v>45082</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>2619</v>
       </c>
@@ -27378,7 +27379,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>2626</v>
       </c>
@@ -27407,7 +27408,7 @@
         <v>2633</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>2634</v>
       </c>
@@ -27453,7 +27454,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>2645</v>
       </c>
@@ -27482,7 +27483,7 @@
         <v>45516</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>2652</v>
       </c>
@@ -27511,7 +27512,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>2659</v>
       </c>
@@ -27557,7 +27558,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>2671</v>
       </c>
@@ -27597,7 +27598,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>2680</v>
       </c>
@@ -27643,7 +27644,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>2691</v>
       </c>
@@ -27672,7 +27673,7 @@
         <v>43257</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>2698</v>
       </c>
@@ -27701,7 +27702,7 @@
         <v>44884</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>2705</v>
       </c>
@@ -27730,7 +27731,7 @@
         <v>45175</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>2712</v>
       </c>
@@ -27759,7 +27760,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>2712</v>
       </c>
@@ -27788,7 +27789,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>2712</v>
       </c>
@@ -27817,7 +27818,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>2712</v>
       </c>
@@ -27846,7 +27847,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>2712</v>
       </c>
@@ -27875,7 +27876,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>2712</v>
       </c>
@@ -27904,7 +27905,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>2712</v>
       </c>
@@ -27933,7 +27934,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>2712</v>
       </c>
@@ -27962,7 +27963,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>2712</v>
       </c>
@@ -28008,7 +28009,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>2730</v>
       </c>
@@ -28037,7 +28038,7 @@
         <v>44977</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>2737</v>
       </c>
@@ -28100,7 +28101,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>2754</v>
       </c>
@@ -28129,7 +28130,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>2754</v>
       </c>
@@ -28158,7 +28159,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>2754</v>
       </c>
@@ -28187,7 +28188,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>2754</v>
       </c>
@@ -28216,7 +28217,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>2754</v>
       </c>
@@ -28245,7 +28246,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>2754</v>
       </c>
@@ -28274,7 +28275,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>2754</v>
       </c>
@@ -28303,7 +28304,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>2754</v>
       </c>
@@ -28332,7 +28333,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>2754</v>
       </c>
@@ -28361,7 +28362,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>2759</v>
       </c>
@@ -28407,7 +28408,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>2771</v>
       </c>
@@ -28436,7 +28437,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>2771</v>
       </c>
@@ -28465,7 +28466,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>2771</v>
       </c>
@@ -28494,7 +28495,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>2771</v>
       </c>
@@ -28574,7 +28575,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>2792</v>
       </c>
@@ -28603,7 +28604,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>2799</v>
       </c>
@@ -28632,7 +28633,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>2807</v>
       </c>
@@ -28661,7 +28662,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>2815</v>
       </c>
@@ -28690,7 +28691,7 @@
         <v>44904</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>2822</v>
       </c>
@@ -28719,7 +28720,7 @@
         <v>44516</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>2829</v>
       </c>
@@ -28765,7 +28766,7 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>2840</v>
       </c>
@@ -28794,7 +28795,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>2840</v>
       </c>
@@ -28823,7 +28824,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>2840</v>
       </c>
@@ -28852,7 +28853,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>2840</v>
       </c>
@@ -28915,7 +28916,7 @@
         <v>45988</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>2859</v>
       </c>
@@ -28961,7 +28962,7 @@
         <v>45896</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>2870</v>
       </c>
@@ -28990,7 +28991,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>2870</v>
       </c>
@@ -29019,7 +29020,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>2870</v>
       </c>
@@ -29048,7 +29049,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>2870</v>
       </c>
@@ -29077,7 +29078,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>2881</v>
       </c>
@@ -29123,7 +29124,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>2892</v>
       </c>
@@ -29152,7 +29153,7 @@
         <v>45291</v>
       </c>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>2899</v>
       </c>
@@ -29181,7 +29182,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>2906</v>
       </c>
@@ -29221,7 +29222,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>2914</v>
       </c>
@@ -29250,7 +29251,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>2921</v>
       </c>
@@ -29330,7 +29331,7 @@
         <v>45636</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>2941</v>
       </c>
@@ -29359,7 +29360,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>2941</v>
       </c>
@@ -29388,7 +29389,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>2941</v>
       </c>
@@ -29417,7 +29418,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>2941</v>
       </c>
@@ -29446,7 +29447,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>2941</v>
       </c>
@@ -29475,7 +29476,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>2941</v>
       </c>
@@ -29504,7 +29505,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>2941</v>
       </c>
@@ -29533,7 +29534,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>2941</v>
       </c>
@@ -29562,7 +29563,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>2941</v>
       </c>
@@ -29591,7 +29592,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>2954</v>
       </c>
@@ -29620,7 +29621,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>2961</v>
       </c>
@@ -29666,7 +29667,7 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>2972</v>
       </c>
@@ -29695,7 +29696,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>2979</v>
       </c>
@@ -29724,7 +29725,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>2983</v>
       </c>
@@ -29753,7 +29754,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>2990</v>
       </c>
@@ -29782,7 +29783,7 @@
         <v>43069</v>
       </c>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>2997</v>
       </c>
@@ -29828,7 +29829,7 @@
         <v>3008</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>3009</v>
       </c>
@@ -29857,7 +29858,7 @@
         <v>44795</v>
       </c>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>3016</v>
       </c>
@@ -29886,7 +29887,7 @@
         <v>45540</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>3023</v>
       </c>
@@ -29932,7 +29933,7 @@
         <v>45028</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>3034</v>
       </c>
@@ -29961,7 +29962,7 @@
         <v>44246</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>3041</v>
       </c>
@@ -29990,7 +29991,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>3048</v>
       </c>
@@ -30019,7 +30020,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>3055</v>
       </c>
@@ -30048,7 +30049,7 @@
         <v>45547</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>3062</v>
       </c>
@@ -30077,7 +30078,7 @@
         <v>3069</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>3070</v>
       </c>
@@ -30106,7 +30107,7 @@
         <v>44749</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>3077</v>
       </c>
@@ -30135,7 +30136,7 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>3084</v>
       </c>
@@ -30164,7 +30165,7 @@
         <v>44749</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>3091</v>
       </c>
@@ -30193,7 +30194,7 @@
         <v>44363</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>3098</v>
       </c>
@@ -30239,7 +30240,7 @@
         <v>43132</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>3110</v>
       </c>
@@ -30268,7 +30269,7 @@
         <v>43885</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>3117</v>
       </c>
@@ -30297,7 +30298,7 @@
         <v>44733</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>3124</v>
       </c>
@@ -30326,7 +30327,7 @@
         <v>43305</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>3130</v>
       </c>
@@ -30355,7 +30356,7 @@
         <v>44657</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>3130</v>
       </c>
@@ -30384,7 +30385,7 @@
         <v>44657</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>3134</v>
       </c>
@@ -30413,7 +30414,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>3141</v>
       </c>
@@ -30442,7 +30443,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>3148</v>
       </c>
@@ -30471,7 +30472,7 @@
         <v>43489</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>3155</v>
       </c>
@@ -30500,7 +30501,7 @@
         <v>43489</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>3159</v>
       </c>
@@ -30529,7 +30530,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>3166</v>
       </c>
@@ -30558,7 +30559,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>3166</v>
       </c>
@@ -30587,7 +30588,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>3166</v>
       </c>
@@ -30616,7 +30617,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>3166</v>
       </c>
@@ -30662,7 +30663,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>3174</v>
       </c>
@@ -30725,7 +30726,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>3189</v>
       </c>
@@ -30754,7 +30755,7 @@
         <v>42991</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>3196</v>
       </c>
@@ -30783,7 +30784,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>3196</v>
       </c>
@@ -30812,7 +30813,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>3196</v>
       </c>
@@ -30841,7 +30842,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>3196</v>
       </c>
@@ -30870,7 +30871,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>3196</v>
       </c>
@@ -30899,7 +30900,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>3196</v>
       </c>
@@ -30928,7 +30929,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>3196</v>
       </c>
@@ -30957,7 +30958,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>3196</v>
       </c>
@@ -30986,7 +30987,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>3196</v>
       </c>
@@ -31032,7 +31033,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>3212</v>
       </c>
@@ -31061,7 +31062,7 @@
         <v>44617</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>3219</v>
       </c>
@@ -31090,7 +31091,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>3226</v>
       </c>
@@ -31119,7 +31120,7 @@
         <v>44764</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>3233</v>
       </c>
@@ -31148,7 +31149,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>3240</v>
       </c>
@@ -31177,7 +31178,7 @@
         <v>45133</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>3247</v>
       </c>
@@ -31206,7 +31207,7 @@
         <v>3253</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>3254</v>
       </c>
@@ -31235,7 +31236,7 @@
         <v>3261</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>3262</v>
       </c>
@@ -31264,7 +31265,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>3262</v>
       </c>
@@ -31293,7 +31294,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>3262</v>
       </c>
@@ -31322,7 +31323,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>3262</v>
       </c>
@@ -31351,7 +31352,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>3269</v>
       </c>
@@ -31380,7 +31381,7 @@
         <v>42044</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>3276</v>
       </c>
@@ -31409,7 +31410,7 @@
         <v>45079</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>3283</v>
       </c>
@@ -31438,7 +31439,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>3290</v>
       </c>
@@ -31467,7 +31468,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>3295</v>
       </c>
@@ -31513,7 +31514,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>3303</v>
       </c>
@@ -31542,7 +31543,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>3310</v>
       </c>
@@ -31571,7 +31572,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>3317</v>
       </c>
@@ -31634,7 +31635,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>3332</v>
       </c>
@@ -31663,7 +31664,7 @@
         <v>3339</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>3340</v>
       </c>
@@ -31709,7 +31710,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>3351</v>
       </c>
@@ -31738,7 +31739,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>3358</v>
       </c>
@@ -31784,7 +31785,7 @@
         <v>3369</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>3370</v>
       </c>
@@ -31813,7 +31814,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>3377</v>
       </c>
@@ -31842,7 +31843,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>3377</v>
       </c>
@@ -31871,7 +31872,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>3377</v>
       </c>
@@ -31933,7 +31934,7 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>3391</v>
       </c>
@@ -31962,7 +31963,7 @@
         <v>41499</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>3397</v>
       </c>
@@ -32008,7 +32009,7 @@
         <v>44544</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>3407</v>
       </c>
@@ -32037,7 +32038,7 @@
         <v>3414</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>3415</v>
       </c>
@@ -32066,7 +32067,7 @@
         <v>44508</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>3422</v>
       </c>
@@ -32112,7 +32113,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>3433</v>
       </c>
@@ -32141,7 +32142,7 @@
         <v>42536</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>3440</v>
       </c>
@@ -32170,7 +32171,7 @@
         <v>43837</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>3447</v>
       </c>
@@ -32199,7 +32200,7 @@
         <v>3454</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>3455</v>
       </c>
@@ -32228,7 +32229,7 @@
         <v>43801</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>3462</v>
       </c>
@@ -32257,7 +32258,7 @@
         <v>44747</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>3469</v>
       </c>
@@ -32286,7 +32287,7 @@
         <v>44501</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>3476</v>
       </c>
@@ -32315,7 +32316,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>3481</v>
       </c>
@@ -32344,7 +32345,7 @@
         <v>45133</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>3485</v>
       </c>
@@ -32373,7 +32374,7 @@
         <v>43662</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>3492</v>
       </c>
@@ -32402,7 +32403,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>3496</v>
       </c>
@@ -32431,7 +32432,7 @@
         <v>45484</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>3503</v>
       </c>
@@ -32460,7 +32461,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>3511</v>
       </c>
@@ -32489,7 +32490,7 @@
         <v>44545</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>3515</v>
       </c>
@@ -32535,7 +32536,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>3527</v>
       </c>
@@ -32564,7 +32565,7 @@
         <v>3531</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>3532</v>
       </c>
@@ -32615,7 +32616,7 @@
         <v>3541</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>3542</v>
       </c>
@@ -32641,7 +32642,7 @@
         <v>3547</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>3542</v>
       </c>
@@ -32667,7 +32668,7 @@
         <v>3547</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>3549</v>
       </c>
@@ -32707,7 +32708,7 @@
         <v>3556</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>3557</v>
       </c>
@@ -32736,7 +32737,7 @@
         <v>43878</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>3561</v>
       </c>
@@ -32765,7 +32766,7 @@
         <v>43332</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>3568</v>
       </c>
@@ -32794,7 +32795,7 @@
         <v>3575</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>3576</v>
       </c>
@@ -32823,7 +32824,7 @@
         <v>3583</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>3584</v>
       </c>
@@ -32852,7 +32853,7 @@
         <v>43867</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>3591</v>
       </c>
@@ -32915,7 +32916,7 @@
         <v>45236</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>3606</v>
       </c>
@@ -32995,7 +32996,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>3626</v>
       </c>
@@ -33024,7 +33025,7 @@
         <v>45616</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>3633</v>
       </c>
@@ -33081,7 +33082,7 @@
         <v>3647</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>3648</v>
       </c>
@@ -33110,7 +33111,7 @@
         <v>3652</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>3653</v>
       </c>
@@ -33139,7 +33140,7 @@
         <v>45036</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>3660</v>
       </c>
@@ -33202,7 +33203,7 @@
         <v>44021</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>3675</v>
       </c>
@@ -33231,7 +33232,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>3682</v>
       </c>
@@ -33260,7 +33261,7 @@
         <v>3689</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>3690</v>
       </c>
@@ -33323,7 +33324,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>3705</v>
       </c>
@@ -33352,7 +33353,7 @@
         <v>43119</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>3711</v>
       </c>
@@ -33381,7 +33382,7 @@
         <v>45163</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>3718</v>
       </c>
@@ -33410,7 +33411,7 @@
         <v>44879</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>3725</v>
       </c>
@@ -33439,7 +33440,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>3725</v>
       </c>
@@ -33468,7 +33469,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>3725</v>
       </c>
@@ -33497,7 +33498,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>3725</v>
       </c>
@@ -33554,7 +33555,7 @@
         <v>3735</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>3736</v>
       </c>
@@ -33583,7 +33584,7 @@
         <v>41800</v>
       </c>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>3740</v>
       </c>
@@ -33612,7 +33613,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>3740</v>
       </c>
@@ -33641,7 +33642,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>3740</v>
       </c>
@@ -33670,7 +33671,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>3740</v>
       </c>
@@ -33699,7 +33700,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>3750</v>
       </c>
@@ -33750,7 +33751,7 @@
         <v>3762</v>
       </c>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>3763</v>
       </c>
@@ -33779,7 +33780,7 @@
         <v>43885</v>
       </c>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>3770</v>
       </c>
@@ -33808,7 +33809,7 @@
         <v>43885</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>3777</v>
       </c>
@@ -33837,7 +33838,7 @@
         <v>44970</v>
       </c>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>3782</v>
       </c>
@@ -33866,7 +33867,7 @@
         <v>44970</v>
       </c>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>3789</v>
       </c>
@@ -33895,7 +33896,7 @@
         <v>44970</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>3791</v>
       </c>
@@ -33941,7 +33942,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>3799</v>
       </c>
@@ -33970,7 +33971,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>3807</v>
       </c>
@@ -33999,7 +34000,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>3807</v>
       </c>
@@ -34028,7 +34029,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>3807</v>
       </c>
@@ -34057,7 +34058,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>3807</v>
       </c>
@@ -34086,7 +34087,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>3814</v>
       </c>
@@ -34115,7 +34116,7 @@
         <v>44585</v>
       </c>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>3821</v>
       </c>
@@ -34144,7 +34145,7 @@
         <v>45173</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>3828</v>
       </c>
@@ -34173,7 +34174,7 @@
         <v>43481</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>3835</v>
       </c>
@@ -34202,7 +34203,7 @@
         <v>43788</v>
       </c>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>3842</v>
       </c>
@@ -34231,7 +34232,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>3849</v>
       </c>
@@ -34260,7 +34261,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>3849</v>
       </c>
@@ -34289,7 +34290,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>3849</v>
       </c>
@@ -34318,7 +34319,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>3849</v>
       </c>
@@ -34347,7 +34348,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>3858</v>
       </c>
@@ -34393,7 +34394,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>3869</v>
       </c>
@@ -34422,7 +34423,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>3869</v>
       </c>
@@ -34451,7 +34452,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>3869</v>
       </c>
@@ -34480,7 +34481,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>3869</v>
       </c>
@@ -34509,7 +34510,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>3869</v>
       </c>
@@ -34538,7 +34539,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>3869</v>
       </c>
@@ -34567,7 +34568,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>3869</v>
       </c>
@@ -34596,7 +34597,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>3869</v>
       </c>
@@ -34625,7 +34626,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>3869</v>
       </c>
@@ -34654,7 +34655,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>3881</v>
       </c>
@@ -34683,7 +34684,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>3885</v>
       </c>
@@ -34712,7 +34713,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>3889</v>
       </c>
@@ -34741,7 +34742,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>3896</v>
       </c>
@@ -34770,7 +34771,7 @@
         <v>44180</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>3896</v>
       </c>
@@ -34799,7 +34800,7 @@
         <v>44180</v>
       </c>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>3896</v>
       </c>
@@ -34828,7 +34829,7 @@
         <v>44180</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>3896</v>
       </c>
@@ -34874,7 +34875,7 @@
         <v>44180</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>3907</v>
       </c>
@@ -34920,7 +34921,7 @@
         <v>3918</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>3919</v>
       </c>
@@ -34949,7 +34950,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>3925</v>
       </c>
@@ -34978,7 +34979,7 @@
         <v>44222</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>3932</v>
       </c>
@@ -35007,7 +35008,7 @@
         <v>43773</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>3939</v>
       </c>
@@ -35036,7 +35037,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>3946</v>
       </c>
@@ -35065,7 +35066,7 @@
         <v>43923</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>3953</v>
       </c>
@@ -35094,7 +35095,7 @@
         <v>43950</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>3960</v>
       </c>
@@ -35123,7 +35124,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>3967</v>
       </c>
@@ -35152,7 +35153,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>3974</v>
       </c>
@@ -35198,7 +35199,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>3986</v>
       </c>
@@ -35227,7 +35228,7 @@
         <v>43049</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>3993</v>
       </c>
@@ -35256,7 +35257,7 @@
         <v>44201</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>4000</v>
       </c>
@@ -35285,7 +35286,7 @@
         <v>4007</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>4008</v>
       </c>
@@ -35314,7 +35315,7 @@
         <v>42710</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>4008</v>
       </c>
@@ -35343,7 +35344,7 @@
         <v>42710</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>4008</v>
       </c>
@@ -35372,7 +35373,7 @@
         <v>42710</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>4008</v>
       </c>
@@ -35401,7 +35402,7 @@
         <v>42710</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>4018</v>
       </c>
@@ -35430,7 +35431,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>4025</v>
       </c>
@@ -35459,7 +35460,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>4029</v>
       </c>
@@ -35488,7 +35489,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>4033</v>
       </c>
@@ -35517,7 +35518,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>4037</v>
       </c>
@@ -35546,7 +35547,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>4041</v>
       </c>
@@ -35575,7 +35576,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>4045</v>
       </c>
@@ -35604,7 +35605,7 @@
         <v>42831</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>4049</v>
       </c>
@@ -35633,7 +35634,7 @@
         <v>44244</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>4053</v>
       </c>
@@ -35662,7 +35663,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>4060</v>
       </c>
@@ -35691,7 +35692,7 @@
         <v>44224</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>4067</v>
       </c>
@@ -35771,7 +35772,7 @@
         <v>4087</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>4088</v>
       </c>
@@ -35800,7 +35801,7 @@
         <v>45103</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>4092</v>
       </c>
@@ -35829,7 +35830,7 @@
         <v>43490</v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>4099</v>
       </c>
@@ -35858,7 +35859,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>4099</v>
       </c>
@@ -35887,7 +35888,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>4099</v>
       </c>
@@ -35916,7 +35917,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>4099</v>
       </c>
@@ -35945,7 +35946,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>4109</v>
       </c>
@@ -35991,7 +35992,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>4120</v>
       </c>
@@ -36020,7 +36021,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>4127</v>
       </c>
@@ -36049,7 +36050,7 @@
         <v>43320</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>4134</v>
       </c>
@@ -36112,7 +36113,7 @@
         <v>3613</v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>4149</v>
       </c>
@@ -36142,6 +36143,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I887" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Lesson_development/merged_dataset_ref_with_doi.xlsx
+++ b/Lesson_development/merged_dataset_ref_with_doi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/linigodelacruz_tudelft_nl/Documents/Documents/4TU.ResearchData/Projects/TRAINING/WebAPI_with_uses_cases/USES-CASES/Sync_Pure_4TU_WUR/Lesson_development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="11_76A953B3D350DFA180E81DD04B5ED87656C67458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58F17F5E-68A7-4083-8D4E-5484B8052623}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_76A953B3D350DFA180E81DD04B5ED87656C67458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F846F967-2C4E-41CB-AA27-1F96AA527C55}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12873,7 +12873,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I887"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12917,7 +12916,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -12946,7 +12945,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -12975,7 +12974,7 @@
         <v>45197</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -13331,7 +13330,7 @@
         <v>44426</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>100</v>
       </c>
@@ -13360,7 +13359,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>108</v>
       </c>
@@ -13389,7 +13388,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>117</v>
       </c>
@@ -13418,7 +13417,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>121</v>
       </c>
@@ -13447,7 +13446,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>125</v>
       </c>
@@ -13612,7 +13611,7 @@
         <v>45460</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>162</v>
       </c>
@@ -13641,7 +13640,7 @@
         <v>44545</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>169</v>
       </c>
@@ -13670,7 +13669,7 @@
         <v>44502</v>
       </c>
     </row>
-    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>176</v>
       </c>
@@ -13716,7 +13715,7 @@
         <v>43105</v>
       </c>
     </row>
-    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>187</v>
       </c>
@@ -13745,7 +13744,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>194</v>
       </c>
@@ -13774,7 +13773,7 @@
         <v>46072</v>
       </c>
     </row>
-    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>202</v>
       </c>
@@ -13803,7 +13802,7 @@
         <v>45238</v>
       </c>
     </row>
-    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>209</v>
       </c>
@@ -13832,7 +13831,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>216</v>
       </c>
@@ -13861,7 +13860,7 @@
         <v>44760</v>
       </c>
     </row>
-    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>223</v>
       </c>
@@ -13887,7 +13886,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>223</v>
       </c>
@@ -13913,7 +13912,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>223</v>
       </c>
@@ -13942,7 +13941,7 @@
         <v>44385</v>
       </c>
     </row>
-    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>223</v>
       </c>
@@ -13988,7 +13987,7 @@
         <v>45541</v>
       </c>
     </row>
-    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>237</v>
       </c>
@@ -14017,7 +14016,7 @@
         <v>45607</v>
       </c>
     </row>
-    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>244</v>
       </c>
@@ -14046,7 +14045,7 @@
         <v>43269</v>
       </c>
     </row>
-    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>250</v>
       </c>
@@ -14075,7 +14074,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>250</v>
       </c>
@@ -14104,7 +14103,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>250</v>
       </c>
@@ -14133,7 +14132,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>250</v>
       </c>
@@ -14162,7 +14161,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>250</v>
       </c>
@@ -14191,7 +14190,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>250</v>
       </c>
@@ -14220,7 +14219,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>250</v>
       </c>
@@ -14249,7 +14248,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>250</v>
       </c>
@@ -14278,7 +14277,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>250</v>
       </c>
@@ -14307,7 +14306,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>250</v>
       </c>
@@ -14336,7 +14335,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>250</v>
       </c>
@@ -14365,7 +14364,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>250</v>
       </c>
@@ -14394,7 +14393,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>250</v>
       </c>
@@ -14423,7 +14422,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>250</v>
       </c>
@@ -14452,7 +14451,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>250</v>
       </c>
@@ -14481,7 +14480,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>250</v>
       </c>
@@ -14510,7 +14509,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>250</v>
       </c>
@@ -14539,7 +14538,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>250</v>
       </c>
@@ -14568,7 +14567,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>250</v>
       </c>
@@ -14597,7 +14596,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>250</v>
       </c>
@@ -14626,7 +14625,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>250</v>
       </c>
@@ -14655,7 +14654,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>250</v>
       </c>
@@ -14684,7 +14683,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>250</v>
       </c>
@@ -14713,7 +14712,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>250</v>
       </c>
@@ -14742,7 +14741,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>250</v>
       </c>
@@ -14805,7 +14804,7 @@
         <v>44063</v>
       </c>
     </row>
-    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>279</v>
       </c>
@@ -14834,7 +14833,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>279</v>
       </c>
@@ -14863,7 +14862,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>279</v>
       </c>
@@ -14892,7 +14891,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>279</v>
       </c>
@@ -14921,7 +14920,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>289</v>
       </c>
@@ -14950,7 +14949,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>296</v>
       </c>
@@ -14979,7 +14978,7 @@
         <v>42831</v>
       </c>
     </row>
-    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>303</v>
       </c>
@@ -15008,7 +15007,7 @@
         <v>44300</v>
       </c>
     </row>
-    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>303</v>
       </c>
@@ -15037,7 +15036,7 @@
         <v>44300</v>
       </c>
     </row>
-    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>303</v>
       </c>
@@ -15063,7 +15062,7 @@
         <v>44300</v>
       </c>
     </row>
-    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>303</v>
       </c>
@@ -15089,7 +15088,7 @@
         <v>44300</v>
       </c>
     </row>
-    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>312</v>
       </c>
@@ -15118,7 +15117,7 @@
         <v>44526</v>
       </c>
     </row>
-    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>316</v>
       </c>
@@ -15147,7 +15146,7 @@
         <v>43993</v>
       </c>
     </row>
-    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>323</v>
       </c>
@@ -15193,7 +15192,7 @@
         <v>44615</v>
       </c>
     </row>
-    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>334</v>
       </c>
@@ -15222,7 +15221,7 @@
         <v>42678</v>
       </c>
     </row>
-    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>341</v>
       </c>
@@ -15285,7 +15284,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>359</v>
       </c>
@@ -15314,7 +15313,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>359</v>
       </c>
@@ -15343,7 +15342,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>359</v>
       </c>
@@ -15372,7 +15371,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>359</v>
       </c>
@@ -15401,7 +15400,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>359</v>
       </c>
@@ -15430,7 +15429,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>359</v>
       </c>
@@ -15459,7 +15458,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>359</v>
       </c>
@@ -15488,7 +15487,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>359</v>
       </c>
@@ -15517,7 +15516,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>359</v>
       </c>
@@ -15546,7 +15545,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>359</v>
       </c>
@@ -15572,7 +15571,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>359</v>
       </c>
@@ -15598,7 +15597,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>359</v>
       </c>
@@ -15627,7 +15626,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>359</v>
       </c>
@@ -15656,7 +15655,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>359</v>
       </c>
@@ -15685,7 +15684,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>359</v>
       </c>
@@ -15714,7 +15713,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>359</v>
       </c>
@@ -15743,7 +15742,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>359</v>
       </c>
@@ -15772,7 +15771,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>359</v>
       </c>
@@ -15798,7 +15797,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>359</v>
       </c>
@@ -15824,7 +15823,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>359</v>
       </c>
@@ -15853,7 +15852,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>359</v>
       </c>
@@ -15882,7 +15881,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>359</v>
       </c>
@@ -15911,7 +15910,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>359</v>
       </c>
@@ -15940,7 +15939,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>359</v>
       </c>
@@ -15969,7 +15968,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>359</v>
       </c>
@@ -15998,7 +15997,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>359</v>
       </c>
@@ -16027,7 +16026,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>359</v>
       </c>
@@ -16056,7 +16055,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>359</v>
       </c>
@@ -16085,7 +16084,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>359</v>
       </c>
@@ -16114,7 +16113,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>359</v>
       </c>
@@ -16143,7 +16142,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>359</v>
       </c>
@@ -16172,7 +16171,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>359</v>
       </c>
@@ -16201,7 +16200,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>359</v>
       </c>
@@ -16230,7 +16229,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>359</v>
       </c>
@@ -16259,7 +16258,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>359</v>
       </c>
@@ -16288,7 +16287,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>359</v>
       </c>
@@ -16317,7 +16316,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>359</v>
       </c>
@@ -16346,7 +16345,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>359</v>
       </c>
@@ -16375,7 +16374,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>359</v>
       </c>
@@ -16404,7 +16403,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>359</v>
       </c>
@@ -16433,7 +16432,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>359</v>
       </c>
@@ -16462,7 +16461,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>359</v>
       </c>
@@ -16491,7 +16490,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>359</v>
       </c>
@@ -16520,7 +16519,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>359</v>
       </c>
@@ -16549,7 +16548,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>359</v>
       </c>
@@ -16578,7 +16577,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>359</v>
       </c>
@@ -16607,7 +16606,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>359</v>
       </c>
@@ -16636,7 +16635,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>359</v>
       </c>
@@ -16665,7 +16664,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>359</v>
       </c>
@@ -16694,7 +16693,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>359</v>
       </c>
@@ -16723,7 +16722,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>359</v>
       </c>
@@ -16752,7 +16751,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>359</v>
       </c>
@@ -16781,7 +16780,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>359</v>
       </c>
@@ -16810,7 +16809,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>359</v>
       </c>
@@ -16839,7 +16838,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>359</v>
       </c>
@@ -16868,7 +16867,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>359</v>
       </c>
@@ -16897,7 +16896,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>359</v>
       </c>
@@ -16926,7 +16925,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>359</v>
       </c>
@@ -16955,7 +16954,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>359</v>
       </c>
@@ -16984,7 +16983,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>359</v>
       </c>
@@ -17013,7 +17012,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>359</v>
       </c>
@@ -17042,7 +17041,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>359</v>
       </c>
@@ -17071,7 +17070,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>359</v>
       </c>
@@ -17100,7 +17099,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>359</v>
       </c>
@@ -17129,7 +17128,7 @@
         <v>43794</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>385</v>
       </c>
@@ -17175,7 +17174,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>396</v>
       </c>
@@ -17204,7 +17203,7 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>403</v>
       </c>
@@ -17284,7 +17283,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>425</v>
       </c>
@@ -17313,7 +17312,7 @@
         <v>45887</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>432</v>
       </c>
@@ -17342,7 +17341,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>440</v>
       </c>
@@ -17371,7 +17370,7 @@
         <v>44287</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>447</v>
       </c>
@@ -17400,7 +17399,7 @@
         <v>44350</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>454</v>
       </c>
@@ -17429,7 +17428,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>462</v>
       </c>
@@ -17458,7 +17457,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>470</v>
       </c>
@@ -17504,7 +17503,7 @@
         <v>45559</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>482</v>
       </c>
@@ -17550,7 +17549,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>493</v>
       </c>
@@ -17596,7 +17595,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>504</v>
       </c>
@@ -17625,7 +17624,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>512</v>
       </c>
@@ -17654,7 +17653,7 @@
         <v>45252</v>
       </c>
     </row>
-    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>519</v>
       </c>
@@ -17683,7 +17682,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>527</v>
       </c>
@@ -17729,7 +17728,7 @@
         <v>45315</v>
       </c>
     </row>
-    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>538</v>
       </c>
@@ -17758,7 +17757,7 @@
         <v>45902</v>
       </c>
     </row>
-    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>545</v>
       </c>
@@ -17804,7 +17803,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>557</v>
       </c>
@@ -17867,7 +17866,7 @@
         <v>45565</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>572</v>
       </c>
@@ -17913,7 +17912,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>585</v>
       </c>
@@ -17959,7 +17958,7 @@
         <v>45477</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>596</v>
       </c>
@@ -18005,7 +18004,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>608</v>
       </c>
@@ -18034,7 +18033,7 @@
         <v>43797</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>615</v>
       </c>
@@ -18063,7 +18062,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>622</v>
       </c>
@@ -18092,7 +18091,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>630</v>
       </c>
@@ -18121,7 +18120,7 @@
         <v>46027</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>636</v>
       </c>
@@ -18150,7 +18149,7 @@
         <v>44564</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>643</v>
       </c>
@@ -18179,7 +18178,7 @@
         <v>44551</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>650</v>
       </c>
@@ -18208,7 +18207,7 @@
         <v>44551</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>657</v>
       </c>
@@ -18254,7 +18253,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>668</v>
       </c>
@@ -18300,7 +18299,7 @@
         <v>44516</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>680</v>
       </c>
@@ -18329,7 +18328,7 @@
         <v>44363</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>687</v>
       </c>
@@ -18358,7 +18357,7 @@
         <v>44183</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>694</v>
       </c>
@@ -18387,7 +18386,7 @@
         <v>44516</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>701</v>
       </c>
@@ -18416,7 +18415,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>709</v>
       </c>
@@ -18445,7 +18444,7 @@
         <v>43860</v>
       </c>
     </row>
-    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>716</v>
       </c>
@@ -18474,7 +18473,7 @@
         <v>43860</v>
       </c>
     </row>
-    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>720</v>
       </c>
@@ -18503,7 +18502,7 @@
         <v>43860</v>
       </c>
     </row>
-    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>724</v>
       </c>
@@ -18532,7 +18531,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>728</v>
       </c>
@@ -18561,7 +18560,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>732</v>
       </c>
@@ -18607,7 +18606,7 @@
         <v>42736</v>
       </c>
     </row>
-    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>743</v>
       </c>
@@ -18636,7 +18635,7 @@
         <v>44655</v>
       </c>
     </row>
-    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>750</v>
       </c>
@@ -18665,7 +18664,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>757</v>
       </c>
@@ -18705,7 +18704,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>769</v>
       </c>
@@ -18734,7 +18733,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>777</v>
       </c>
@@ -18763,7 +18762,7 @@
         <v>45273</v>
       </c>
     </row>
-    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>784</v>
       </c>
@@ -18809,7 +18808,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>795</v>
       </c>
@@ -18838,7 +18837,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>803</v>
       </c>
@@ -18878,7 +18877,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>811</v>
       </c>
@@ -18907,7 +18906,7 @@
         <v>43580</v>
       </c>
     </row>
-    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>818</v>
       </c>
@@ -18953,7 +18952,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>829</v>
       </c>
@@ -18982,7 +18981,7 @@
         <v>44607</v>
       </c>
     </row>
-    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>836</v>
       </c>
@@ -19011,7 +19010,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>844</v>
       </c>
@@ -19040,7 +19039,7 @@
         <v>45321</v>
       </c>
     </row>
-    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>844</v>
       </c>
@@ -19103,7 +19102,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>860</v>
       </c>
@@ -19132,7 +19131,7 @@
         <v>44355</v>
       </c>
     </row>
-    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>867</v>
       </c>
@@ -19161,7 +19160,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>867</v>
       </c>
@@ -19190,7 +19189,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>867</v>
       </c>
@@ -19219,7 +19218,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>867</v>
       </c>
@@ -19248,7 +19247,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>875</v>
       </c>
@@ -19277,7 +19276,7 @@
         <v>44147</v>
       </c>
     </row>
-    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>882</v>
       </c>
@@ -19306,7 +19305,7 @@
         <v>44722</v>
       </c>
     </row>
-    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>889</v>
       </c>
@@ -19335,7 +19334,7 @@
         <v>43370</v>
       </c>
     </row>
-    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>896</v>
       </c>
@@ -19381,7 +19380,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>907</v>
       </c>
@@ -19410,7 +19409,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>907</v>
       </c>
@@ -19439,7 +19438,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>907</v>
       </c>
@@ -19468,7 +19467,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>907</v>
       </c>
@@ -19497,7 +19496,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>917</v>
       </c>
@@ -19526,7 +19525,7 @@
         <v>43356</v>
       </c>
     </row>
-    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>924</v>
       </c>
@@ -19572,7 +19571,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>935</v>
       </c>
@@ -19601,7 +19600,7 @@
         <v>43580</v>
       </c>
     </row>
-    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>942</v>
       </c>
@@ -19630,7 +19629,7 @@
         <v>45028</v>
       </c>
     </row>
-    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>949</v>
       </c>
@@ -19659,7 +19658,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>949</v>
       </c>
@@ -19688,7 +19687,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>949</v>
       </c>
@@ -19717,7 +19716,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>949</v>
       </c>
@@ -19746,7 +19745,7 @@
         <v>44679</v>
       </c>
     </row>
-    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>959</v>
       </c>
@@ -19775,7 +19774,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>963</v>
       </c>
@@ -19804,7 +19803,7 @@
         <v>43811</v>
       </c>
     </row>
-    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>970</v>
       </c>
@@ -19833,7 +19832,7 @@
         <v>43368</v>
       </c>
     </row>
-    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>977</v>
       </c>
@@ -19879,7 +19878,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>989</v>
       </c>
@@ -19919,7 +19918,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1001</v>
       </c>
@@ -19948,7 +19947,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1006</v>
       </c>
@@ -20011,7 +20010,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1022</v>
       </c>
@@ -20040,7 +20039,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1022</v>
       </c>
@@ -20069,7 +20068,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1022</v>
       </c>
@@ -20098,7 +20097,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1022</v>
       </c>
@@ -20127,7 +20126,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1022</v>
       </c>
@@ -20156,7 +20155,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1022</v>
       </c>
@@ -20185,7 +20184,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1022</v>
       </c>
@@ -20214,7 +20213,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1022</v>
       </c>
@@ -20243,7 +20242,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1022</v>
       </c>
@@ -20272,7 +20271,7 @@
         <v>43691</v>
       </c>
     </row>
-    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1035</v>
       </c>
@@ -20301,7 +20300,7 @@
         <v>43858</v>
       </c>
     </row>
-    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1042</v>
       </c>
@@ -20330,7 +20329,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1049</v>
       </c>
@@ -20359,7 +20358,7 @@
         <v>43935</v>
       </c>
     </row>
-    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1056</v>
       </c>
@@ -20388,7 +20387,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1064</v>
       </c>
@@ -20417,7 +20416,7 @@
         <v>43846</v>
       </c>
     </row>
-    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1071</v>
       </c>
@@ -20446,7 +20445,7 @@
         <v>45167</v>
       </c>
     </row>
-    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1078</v>
       </c>
@@ -20475,7 +20474,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1085</v>
       </c>
@@ -20504,7 +20503,7 @@
         <v>43668</v>
       </c>
     </row>
-    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1092</v>
       </c>
@@ -20533,7 +20532,7 @@
         <v>46052</v>
       </c>
     </row>
-    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1099</v>
       </c>
@@ -20562,7 +20561,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1099</v>
       </c>
@@ -20591,7 +20590,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1099</v>
       </c>
@@ -20620,7 +20619,7 @@
         <v>44664</v>
       </c>
     </row>
-    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1099</v>
       </c>
@@ -20666,7 +20665,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1114</v>
       </c>
@@ -20695,7 +20694,7 @@
         <v>43522</v>
       </c>
     </row>
-    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1120</v>
       </c>
@@ -20724,7 +20723,7 @@
         <v>44404</v>
       </c>
     </row>
-    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1127</v>
       </c>
@@ -20753,7 +20752,7 @@
         <v>44417</v>
       </c>
     </row>
-    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1134</v>
       </c>
@@ -20782,7 +20781,7 @@
         <v>45329</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1141</v>
       </c>
@@ -20811,7 +20810,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1149</v>
       </c>
@@ -20840,7 +20839,7 @@
         <v>44867</v>
       </c>
     </row>
-    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1156</v>
       </c>
@@ -20869,7 +20868,7 @@
         <v>44942</v>
       </c>
     </row>
-    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1163</v>
       </c>
@@ -20898,7 +20897,7 @@
         <v>44599</v>
       </c>
     </row>
-    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1170</v>
       </c>
@@ -20927,7 +20926,7 @@
         <v>44819</v>
       </c>
     </row>
-    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1177</v>
       </c>
@@ -20956,7 +20955,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1185</v>
       </c>
@@ -20985,7 +20984,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1193</v>
       </c>
@@ -21014,7 +21013,7 @@
         <v>45548</v>
       </c>
     </row>
-    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1200</v>
       </c>
@@ -21060,7 +21059,7 @@
         <v>45649</v>
       </c>
     </row>
-    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1212</v>
       </c>
@@ -21089,7 +21088,7 @@
         <v>45538</v>
       </c>
     </row>
-    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1219</v>
       </c>
@@ -21135,7 +21134,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>1231</v>
       </c>
@@ -21164,7 +21163,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1238</v>
       </c>
@@ -21210,7 +21209,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1249</v>
       </c>
@@ -21273,7 +21272,7 @@
         <v>46050</v>
       </c>
     </row>
-    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1265</v>
       </c>
@@ -21319,7 +21318,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1278</v>
       </c>
@@ -21348,7 +21347,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1286</v>
       </c>
@@ -21394,7 +21393,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1298</v>
       </c>
@@ -21437,7 +21436,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1310</v>
       </c>
@@ -21466,7 +21465,7 @@
         <v>45166</v>
       </c>
     </row>
-    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1317</v>
       </c>
@@ -21512,7 +21511,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1328</v>
       </c>
@@ -21558,7 +21557,7 @@
         <v>45904</v>
       </c>
     </row>
-    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1340</v>
       </c>
@@ -21604,7 +21603,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1351</v>
       </c>
@@ -21633,7 +21632,7 @@
         <v>45168</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1358</v>
       </c>
@@ -21662,7 +21661,7 @@
         <v>45148</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1365</v>
       </c>
@@ -21691,7 +21690,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>1372</v>
       </c>
@@ -21737,7 +21736,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1383</v>
       </c>
@@ -21783,7 +21782,7 @@
         <v>45406</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1394</v>
       </c>
@@ -21829,7 +21828,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1406</v>
       </c>
@@ -21858,7 +21857,7 @@
         <v>45327</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1413</v>
       </c>
@@ -21887,7 +21886,7 @@
         <v>45327</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1420</v>
       </c>
@@ -21916,7 +21915,7 @@
         <v>45327</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1427</v>
       </c>
@@ -21945,7 +21944,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1435</v>
       </c>
@@ -21974,7 +21973,7 @@
         <v>44461</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1442</v>
       </c>
@@ -22003,7 +22002,7 @@
         <v>44442</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1449</v>
       </c>
@@ -22032,7 +22031,7 @@
         <v>44732</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1456</v>
       </c>
@@ -22061,7 +22060,7 @@
         <v>44139</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1463</v>
       </c>
@@ -22090,7 +22089,7 @@
         <v>44363</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>1470</v>
       </c>
@@ -22119,7 +22118,7 @@
         <v>44405</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1477</v>
       </c>
@@ -22148,7 +22147,7 @@
         <v>44881</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1484</v>
       </c>
@@ -22177,7 +22176,7 @@
         <v>44721</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1490</v>
       </c>
@@ -22206,7 +22205,7 @@
         <v>45331</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1497</v>
       </c>
@@ -22235,7 +22234,7 @@
         <v>45608</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1504</v>
       </c>
@@ -22264,7 +22263,7 @@
         <v>45139</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1511</v>
       </c>
@@ -22293,7 +22292,7 @@
         <v>44746</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1518</v>
       </c>
@@ -22322,7 +22321,7 @@
         <v>45405</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1525</v>
       </c>
@@ -22368,7 +22367,7 @@
         <v>44379</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1536</v>
       </c>
@@ -22397,7 +22396,7 @@
         <v>45236</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1543</v>
       </c>
@@ -22426,7 +22425,7 @@
         <v>44250</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1550</v>
       </c>
@@ -22466,7 +22465,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1562</v>
       </c>
@@ -22495,7 +22494,7 @@
         <v>44231</v>
       </c>
     </row>
-    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1565</v>
       </c>
@@ -22524,7 +22523,7 @@
         <v>45639</v>
       </c>
     </row>
-    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1572</v>
       </c>
@@ -22553,7 +22552,7 @@
         <v>45691</v>
       </c>
     </row>
-    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1579</v>
       </c>
@@ -22582,7 +22581,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1587</v>
       </c>
@@ -22611,7 +22610,7 @@
         <v>45085</v>
       </c>
     </row>
-    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1594</v>
       </c>
@@ -22640,7 +22639,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1601</v>
       </c>
@@ -22669,7 +22668,7 @@
         <v>45141</v>
       </c>
     </row>
-    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1608</v>
       </c>
@@ -22698,7 +22697,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1616</v>
       </c>
@@ -22727,7 +22726,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1623</v>
       </c>
@@ -22756,7 +22755,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1631</v>
       </c>
@@ -22785,7 +22784,7 @@
         <v>44798</v>
       </c>
     </row>
-    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1638</v>
       </c>
@@ -22831,7 +22830,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1650</v>
       </c>
@@ -22860,7 +22859,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1658</v>
       </c>
@@ -22889,7 +22888,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1666</v>
       </c>
@@ -22918,7 +22917,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1673</v>
       </c>
@@ -22947,7 +22946,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1681</v>
       </c>
@@ -22976,7 +22975,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1688</v>
       </c>
@@ -23005,7 +23004,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1696</v>
       </c>
@@ -23034,7 +23033,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1696</v>
       </c>
@@ -23063,7 +23062,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1696</v>
       </c>
@@ -23092,7 +23091,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1696</v>
       </c>
@@ -23121,7 +23120,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1706</v>
       </c>
@@ -23150,7 +23149,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1714</v>
       </c>
@@ -23179,7 +23178,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1721</v>
       </c>
@@ -23208,7 +23207,7 @@
         <v>45282</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1728</v>
       </c>
@@ -23237,7 +23236,7 @@
         <v>44305</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1735</v>
       </c>
@@ -23266,7 +23265,7 @@
         <v>44572</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1742</v>
       </c>
@@ -23295,7 +23294,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>1749</v>
       </c>
@@ -23341,7 +23340,7 @@
         <v>45861</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1760</v>
       </c>
@@ -23387,7 +23386,7 @@
         <v>45274</v>
       </c>
     </row>
-    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1771</v>
       </c>
@@ -23433,7 +23432,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>1783</v>
       </c>
@@ -23479,7 +23478,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1795</v>
       </c>
@@ -23542,7 +23541,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1811</v>
       </c>
@@ -23571,7 +23570,7 @@
         <v>45993</v>
       </c>
     </row>
-    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1818</v>
       </c>
@@ -23600,7 +23599,7 @@
         <v>45769</v>
       </c>
     </row>
-    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1825</v>
       </c>
@@ -23629,7 +23628,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>1832</v>
       </c>
@@ -23658,7 +23657,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>1840</v>
       </c>
@@ -23687,7 +23686,7 @@
         <v>44910</v>
       </c>
     </row>
-    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1847</v>
       </c>
@@ -23733,7 +23732,7 @@
         <v>45847</v>
       </c>
     </row>
-    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1858</v>
       </c>
@@ -23762,7 +23761,7 @@
         <v>45490</v>
       </c>
     </row>
-    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1865</v>
       </c>
@@ -23791,7 +23790,7 @@
         <v>45503</v>
       </c>
     </row>
-    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1872</v>
       </c>
@@ -23820,7 +23819,7 @@
         <v>44579</v>
       </c>
     </row>
-    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1872</v>
       </c>
@@ -23849,7 +23848,7 @@
         <v>44579</v>
       </c>
     </row>
-    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1880</v>
       </c>
@@ -23878,7 +23877,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>1880</v>
       </c>
@@ -23907,7 +23906,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>1880</v>
       </c>
@@ -23936,7 +23935,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1880</v>
       </c>
@@ -23993,7 +23992,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>1897</v>
       </c>
@@ -24056,7 +24055,7 @@
         <v>45868</v>
       </c>
     </row>
-    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1912</v>
       </c>
@@ -24085,7 +24084,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1919</v>
       </c>
@@ -24114,7 +24113,7 @@
         <v>45912</v>
       </c>
     </row>
-    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1926</v>
       </c>
@@ -24143,7 +24142,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1934</v>
       </c>
@@ -24189,7 +24188,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>1945</v>
       </c>
@@ -24218,7 +24217,7 @@
         <v>45896</v>
       </c>
     </row>
-    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1952</v>
       </c>
@@ -24247,7 +24246,7 @@
         <v>44368</v>
       </c>
     </row>
-    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1959</v>
       </c>
@@ -24327,7 +24326,7 @@
         <v>45994</v>
       </c>
     </row>
-    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>1978</v>
       </c>
@@ -24356,7 +24355,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1986</v>
       </c>
@@ -24385,7 +24384,7 @@
         <v>45237</v>
       </c>
     </row>
-    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1986</v>
       </c>
@@ -24414,7 +24413,7 @@
         <v>45237</v>
       </c>
     </row>
-    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1986</v>
       </c>
@@ -24443,7 +24442,7 @@
         <v>45237</v>
       </c>
     </row>
-    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1986</v>
       </c>
@@ -24472,7 +24471,7 @@
         <v>45237</v>
       </c>
     </row>
-    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1996</v>
       </c>
@@ -24501,7 +24500,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>2004</v>
       </c>
@@ -24530,7 +24529,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>2012</v>
       </c>
@@ -24559,7 +24558,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>2012</v>
       </c>
@@ -24588,7 +24587,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>2012</v>
       </c>
@@ -24617,7 +24616,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>2012</v>
       </c>
@@ -24646,7 +24645,7 @@
         <v>45449</v>
       </c>
     </row>
-    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>2021</v>
       </c>
@@ -24675,7 +24674,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>2028</v>
       </c>
@@ -24721,7 +24720,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>2040</v>
       </c>
@@ -24750,7 +24749,7 @@
         <v>45708</v>
       </c>
     </row>
-    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>2047</v>
       </c>
@@ -24779,7 +24778,7 @@
         <v>45979</v>
       </c>
     </row>
-    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>2054</v>
       </c>
@@ -24808,7 +24807,7 @@
         <v>2061</v>
       </c>
     </row>
-    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>2062</v>
       </c>
@@ -24854,7 +24853,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>2074</v>
       </c>
@@ -24883,7 +24882,7 @@
         <v>44014</v>
       </c>
     </row>
-    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>2081</v>
       </c>
@@ -24912,7 +24911,7 @@
         <v>44575</v>
       </c>
     </row>
-    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>2088</v>
       </c>
@@ -24958,7 +24957,7 @@
         <v>45846</v>
       </c>
     </row>
-    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>2099</v>
       </c>
@@ -24987,7 +24986,7 @@
         <v>45247</v>
       </c>
     </row>
-    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>2106</v>
       </c>
@@ -25016,7 +25015,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>2113</v>
       </c>
@@ -25045,7 +25044,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>2120</v>
       </c>
@@ -25074,7 +25073,7 @@
         <v>44600</v>
       </c>
     </row>
-    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>2127</v>
       </c>
@@ -25103,7 +25102,7 @@
         <v>44186</v>
       </c>
     </row>
-    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>2134</v>
       </c>
@@ -25132,7 +25131,7 @@
         <v>45471</v>
       </c>
     </row>
-    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>2141</v>
       </c>
@@ -25178,7 +25177,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>2153</v>
       </c>
@@ -25207,7 +25206,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>2161</v>
       </c>
@@ -25270,7 +25269,7 @@
         <v>44931</v>
       </c>
     </row>
-    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>2173</v>
       </c>
@@ -25299,7 +25298,7 @@
         <v>43998</v>
       </c>
     </row>
-    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>2180</v>
       </c>
@@ -25328,7 +25327,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>2187</v>
       </c>
@@ -25357,7 +25356,7 @@
         <v>44825</v>
       </c>
     </row>
-    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>2194</v>
       </c>
@@ -25386,7 +25385,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>2202</v>
       </c>
@@ -25415,7 +25414,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>2209</v>
       </c>
@@ -25444,7 +25443,7 @@
         <v>44963</v>
       </c>
     </row>
-    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>2216</v>
       </c>
@@ -25473,7 +25472,7 @@
         <v>44572</v>
       </c>
     </row>
-    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>2223</v>
       </c>
@@ -25502,7 +25501,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>2223</v>
       </c>
@@ -25531,7 +25530,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>2223</v>
       </c>
@@ -25560,7 +25559,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>2223</v>
       </c>
@@ -25600,7 +25599,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>2235</v>
       </c>
@@ -25629,7 +25628,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>2242</v>
       </c>
@@ -25675,7 +25674,7 @@
         <v>45919</v>
       </c>
     </row>
-    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>2254</v>
       </c>
@@ -25704,7 +25703,7 @@
         <v>45674</v>
       </c>
     </row>
-    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>2261</v>
       </c>
@@ -25733,7 +25732,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>2269</v>
       </c>
@@ -25779,7 +25778,7 @@
         <v>45518</v>
       </c>
     </row>
-    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>2280</v>
       </c>
@@ -25842,7 +25841,7 @@
         <v>46007</v>
       </c>
     </row>
-    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>2296</v>
       </c>
@@ -25871,7 +25870,7 @@
         <v>44796</v>
       </c>
     </row>
-    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>2303</v>
       </c>
@@ -25917,7 +25916,7 @@
         <v>45624</v>
       </c>
     </row>
-    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>2314</v>
       </c>
@@ -25946,7 +25945,7 @@
         <v>2318</v>
       </c>
     </row>
-    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>2319</v>
       </c>
@@ -26009,7 +26008,7 @@
         <v>46041</v>
       </c>
     </row>
-    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>2335</v>
       </c>
@@ -26038,7 +26037,7 @@
         <v>45092</v>
       </c>
     </row>
-    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>2342</v>
       </c>
@@ -26067,7 +26066,7 @@
         <v>45813</v>
       </c>
     </row>
-    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>2349</v>
       </c>
@@ -26096,7 +26095,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>2356</v>
       </c>
@@ -26125,7 +26124,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>2356</v>
       </c>
@@ -26154,7 +26153,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>2356</v>
       </c>
@@ -26183,7 +26182,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>2356</v>
       </c>
@@ -26212,7 +26211,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>2366</v>
       </c>
@@ -26241,7 +26240,7 @@
         <v>45536</v>
       </c>
     </row>
-    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>2373</v>
       </c>
@@ -26304,7 +26303,7 @@
         <v>46010</v>
       </c>
     </row>
-    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>2388</v>
       </c>
@@ -26333,7 +26332,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>2395</v>
       </c>
@@ -26362,7 +26361,7 @@
         <v>44029</v>
       </c>
     </row>
-    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>2402</v>
       </c>
@@ -26391,7 +26390,7 @@
         <v>46015</v>
       </c>
     </row>
-    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>2409</v>
       </c>
@@ -26420,7 +26419,7 @@
         <v>2416</v>
       </c>
     </row>
-    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>2417</v>
       </c>
@@ -26449,7 +26448,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>2425</v>
       </c>
@@ -26478,7 +26477,7 @@
         <v>45632</v>
       </c>
     </row>
-    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>2432</v>
       </c>
@@ -26507,7 +26506,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>2439</v>
       </c>
@@ -26536,7 +26535,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>2439</v>
       </c>
@@ -26565,7 +26564,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>2439</v>
       </c>
@@ -26594,7 +26593,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>2439</v>
       </c>
@@ -26623,7 +26622,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>2449</v>
       </c>
@@ -26663,7 +26662,7 @@
         <v>2456</v>
       </c>
     </row>
-    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>2457</v>
       </c>
@@ -26692,7 +26691,7 @@
         <v>44830</v>
       </c>
     </row>
-    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>2464</v>
       </c>
@@ -26738,7 +26737,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>2475</v>
       </c>
@@ -26784,7 +26783,7 @@
         <v>45856</v>
       </c>
     </row>
-    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>2486</v>
       </c>
@@ -26813,7 +26812,7 @@
         <v>44203</v>
       </c>
     </row>
-    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>2493</v>
       </c>
@@ -26859,7 +26858,7 @@
         <v>45842</v>
       </c>
     </row>
-    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>2504</v>
       </c>
@@ -26888,7 +26887,7 @@
         <v>2511</v>
       </c>
     </row>
-    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>2512</v>
       </c>
@@ -26917,7 +26916,7 @@
         <v>45534</v>
       </c>
     </row>
-    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>2519</v>
       </c>
@@ -26963,7 +26962,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>2531</v>
       </c>
@@ -27009,7 +27008,7 @@
         <v>45978</v>
       </c>
     </row>
-    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>2542</v>
       </c>
@@ -27038,7 +27037,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>2550</v>
       </c>
@@ -27067,7 +27066,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>2554</v>
       </c>
@@ -27096,7 +27095,7 @@
         <v>2549</v>
       </c>
     </row>
-    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>2558</v>
       </c>
@@ -27159,7 +27158,7 @@
         <v>46079</v>
       </c>
     </row>
-    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>2573</v>
       </c>
@@ -27188,7 +27187,7 @@
         <v>46035</v>
       </c>
     </row>
-    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>2580</v>
       </c>
@@ -27217,7 +27216,7 @@
         <v>45240</v>
       </c>
     </row>
-    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>2587</v>
       </c>
@@ -27246,7 +27245,7 @@
         <v>44557</v>
       </c>
     </row>
-    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>2594</v>
       </c>
@@ -27275,7 +27274,7 @@
         <v>45520</v>
       </c>
     </row>
-    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>2601</v>
       </c>
@@ -27321,7 +27320,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>2612</v>
       </c>
@@ -27350,7 +27349,7 @@
         <v>45082</v>
       </c>
     </row>
-    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>2619</v>
       </c>
@@ -27379,7 +27378,7 @@
         <v>45294</v>
       </c>
     </row>
-    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>2626</v>
       </c>
@@ -27408,7 +27407,7 @@
         <v>2633</v>
       </c>
     </row>
-    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>2634</v>
       </c>
@@ -27454,7 +27453,7 @@
         <v>46043</v>
       </c>
     </row>
-    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>2645</v>
       </c>
@@ -27483,7 +27482,7 @@
         <v>45516</v>
       </c>
     </row>
-    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>2652</v>
       </c>
@@ -27512,7 +27511,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>2659</v>
       </c>
@@ -27558,7 +27557,7 @@
         <v>46045</v>
       </c>
     </row>
-    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>2671</v>
       </c>
@@ -27598,7 +27597,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>2680</v>
       </c>
@@ -27644,7 +27643,7 @@
         <v>45880</v>
       </c>
     </row>
-    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>2691</v>
       </c>
@@ -27673,7 +27672,7 @@
         <v>43257</v>
       </c>
     </row>
-    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>2698</v>
       </c>
@@ -27702,7 +27701,7 @@
         <v>44884</v>
       </c>
     </row>
-    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>2705</v>
       </c>
@@ -27731,7 +27730,7 @@
         <v>45175</v>
       </c>
     </row>
-    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>2712</v>
       </c>
@@ -27760,7 +27759,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>2712</v>
       </c>
@@ -27789,7 +27788,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>2712</v>
       </c>
@@ -27818,7 +27817,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>2712</v>
       </c>
@@ -27847,7 +27846,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>2712</v>
       </c>
@@ -27876,7 +27875,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>2712</v>
       </c>
@@ -27905,7 +27904,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>2712</v>
       </c>
@@ -27934,7 +27933,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>2712</v>
       </c>
@@ -27963,7 +27962,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>2712</v>
       </c>
@@ -28009,7 +28008,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>2730</v>
       </c>
@@ -28038,7 +28037,7 @@
         <v>44977</v>
       </c>
     </row>
-    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>2737</v>
       </c>
@@ -28101,7 +28100,7 @@
         <v>2753</v>
       </c>
     </row>
-    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>2754</v>
       </c>
@@ -28130,7 +28129,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>2754</v>
       </c>
@@ -28159,7 +28158,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>2754</v>
       </c>
@@ -28188,7 +28187,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>2754</v>
       </c>
@@ -28217,7 +28216,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>2754</v>
       </c>
@@ -28246,7 +28245,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>2754</v>
       </c>
@@ -28275,7 +28274,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>2754</v>
       </c>
@@ -28304,7 +28303,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>2754</v>
       </c>
@@ -28333,7 +28332,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>2754</v>
       </c>
@@ -28362,7 +28361,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>2759</v>
       </c>
@@ -28408,7 +28407,7 @@
         <v>45628</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>2771</v>
       </c>
@@ -28437,7 +28436,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>2771</v>
       </c>
@@ -28466,7 +28465,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>2771</v>
       </c>
@@ -28495,7 +28494,7 @@
         <v>45637</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>2771</v>
       </c>
@@ -28575,7 +28574,7 @@
         <v>46077</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>2792</v>
       </c>
@@ -28604,7 +28603,7 @@
         <v>1657</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>2799</v>
       </c>
@@ -28633,7 +28632,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>2807</v>
       </c>
@@ -28662,7 +28661,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>2815</v>
       </c>
@@ -28691,7 +28690,7 @@
         <v>44904</v>
       </c>
     </row>
-    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>2822</v>
       </c>
@@ -28720,7 +28719,7 @@
         <v>44516</v>
       </c>
     </row>
-    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>2829</v>
       </c>
@@ -28766,7 +28765,7 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>2840</v>
       </c>
@@ -28795,7 +28794,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>2840</v>
       </c>
@@ -28824,7 +28823,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>2840</v>
       </c>
@@ -28853,7 +28852,7 @@
         <v>45705</v>
       </c>
     </row>
-    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>2840</v>
       </c>
@@ -28916,7 +28915,7 @@
         <v>45988</v>
       </c>
     </row>
-    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>2859</v>
       </c>
@@ -28962,7 +28961,7 @@
         <v>45896</v>
       </c>
     </row>
-    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>2870</v>
       </c>
@@ -28991,7 +28990,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>2870</v>
       </c>
@@ -29020,7 +29019,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>2870</v>
       </c>
@@ -29049,7 +29048,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>2870</v>
       </c>
@@ -29078,7 +29077,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>2881</v>
       </c>
@@ -29124,7 +29123,7 @@
         <v>45663</v>
       </c>
     </row>
-    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>2892</v>
       </c>
@@ -29153,7 +29152,7 @@
         <v>45291</v>
       </c>
     </row>
-    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>2899</v>
       </c>
@@ -29182,7 +29181,7 @@
         <v>45030</v>
       </c>
     </row>
-    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>2906</v>
       </c>
@@ -29222,7 +29221,7 @@
         <v>2913</v>
       </c>
     </row>
-    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>2914</v>
       </c>
@@ -29251,7 +29250,7 @@
         <v>45967</v>
       </c>
     </row>
-    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>2921</v>
       </c>
@@ -29331,7 +29330,7 @@
         <v>45636</v>
       </c>
     </row>
-    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>2941</v>
       </c>
@@ -29360,7 +29359,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>2941</v>
       </c>
@@ -29389,7 +29388,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>2941</v>
       </c>
@@ -29418,7 +29417,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>2941</v>
       </c>
@@ -29447,7 +29446,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>2941</v>
       </c>
@@ -29476,7 +29475,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>2941</v>
       </c>
@@ -29505,7 +29504,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>2941</v>
       </c>
@@ -29534,7 +29533,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>2941</v>
       </c>
@@ -29563,7 +29562,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>2941</v>
       </c>
@@ -29592,7 +29591,7 @@
         <v>45644</v>
       </c>
     </row>
-    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>2954</v>
       </c>
@@ -29621,7 +29620,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>2961</v>
       </c>
@@ -29667,7 +29666,7 @@
         <v>44896</v>
       </c>
     </row>
-    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>2972</v>
       </c>
@@ -29696,7 +29695,7 @@
         <v>45716</v>
       </c>
     </row>
-    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>2979</v>
       </c>
@@ -29725,7 +29724,7 @@
         <v>45408</v>
       </c>
     </row>
-    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>2983</v>
       </c>
@@ -29754,7 +29753,7 @@
         <v>45643</v>
       </c>
     </row>
-    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>2990</v>
       </c>
@@ -29783,7 +29782,7 @@
         <v>43069</v>
       </c>
     </row>
-    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>2997</v>
       </c>
@@ -29829,7 +29828,7 @@
         <v>3008</v>
       </c>
     </row>
-    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>3009</v>
       </c>
@@ -29858,7 +29857,7 @@
         <v>44795</v>
       </c>
     </row>
-    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>3016</v>
       </c>
@@ -29887,7 +29886,7 @@
         <v>45540</v>
       </c>
     </row>
-    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>3023</v>
       </c>
@@ -29933,7 +29932,7 @@
         <v>45028</v>
       </c>
     </row>
-    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>3034</v>
       </c>
@@ -29962,7 +29961,7 @@
         <v>44246</v>
       </c>
     </row>
-    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>3041</v>
       </c>
@@ -29991,7 +29990,7 @@
         <v>44601</v>
       </c>
     </row>
-    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>3048</v>
       </c>
@@ -30020,7 +30019,7 @@
         <v>45385</v>
       </c>
     </row>
-    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>3055</v>
       </c>
@@ -30049,7 +30048,7 @@
         <v>45547</v>
       </c>
     </row>
-    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>3062</v>
       </c>
@@ -30078,7 +30077,7 @@
         <v>3069</v>
       </c>
     </row>
-    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>3070</v>
       </c>
@@ -30107,7 +30106,7 @@
         <v>44749</v>
       </c>
     </row>
-    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>3077</v>
       </c>
@@ -30136,7 +30135,7 @@
         <v>45029</v>
       </c>
     </row>
-    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>3084</v>
       </c>
@@ -30165,7 +30164,7 @@
         <v>44749</v>
       </c>
     </row>
-    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>3091</v>
       </c>
@@ -30194,7 +30193,7 @@
         <v>44363</v>
       </c>
     </row>
-    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>3098</v>
       </c>
@@ -30240,7 +30239,7 @@
         <v>43132</v>
       </c>
     </row>
-    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>3110</v>
       </c>
@@ -30269,7 +30268,7 @@
         <v>43885</v>
       </c>
     </row>
-    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>3117</v>
       </c>
@@ -30298,7 +30297,7 @@
         <v>44733</v>
       </c>
     </row>
-    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>3124</v>
       </c>
@@ -30327,7 +30326,7 @@
         <v>43305</v>
       </c>
     </row>
-    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>3130</v>
       </c>
@@ -30356,7 +30355,7 @@
         <v>44657</v>
       </c>
     </row>
-    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>3130</v>
       </c>
@@ -30385,7 +30384,7 @@
         <v>44657</v>
       </c>
     </row>
-    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>3134</v>
       </c>
@@ -30414,7 +30413,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>3141</v>
       </c>
@@ -30443,7 +30442,7 @@
         <v>45819</v>
       </c>
     </row>
-    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>3148</v>
       </c>
@@ -30472,7 +30471,7 @@
         <v>43489</v>
       </c>
     </row>
-    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>3155</v>
       </c>
@@ -30501,7 +30500,7 @@
         <v>43489</v>
       </c>
     </row>
-    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>3159</v>
       </c>
@@ -30530,7 +30529,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>3166</v>
       </c>
@@ -30559,7 +30558,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>3166</v>
       </c>
@@ -30588,7 +30587,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>3166</v>
       </c>
@@ -30617,7 +30616,7 @@
         <v>45313</v>
       </c>
     </row>
-    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>3166</v>
       </c>
@@ -30663,7 +30662,7 @@
         <v>45391</v>
       </c>
     </row>
-    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>3174</v>
       </c>
@@ -30726,7 +30725,7 @@
         <v>45560</v>
       </c>
     </row>
-    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>3189</v>
       </c>
@@ -30755,7 +30754,7 @@
         <v>42991</v>
       </c>
     </row>
-    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>3196</v>
       </c>
@@ -30784,7 +30783,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>3196</v>
       </c>
@@ -30813,7 +30812,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>3196</v>
       </c>
@@ -30842,7 +30841,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>3196</v>
       </c>
@@ -30871,7 +30870,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>3196</v>
       </c>
@@ -30900,7 +30899,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>3196</v>
       </c>
@@ -30929,7 +30928,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>3196</v>
       </c>
@@ -30958,7 +30957,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>3196</v>
       </c>
@@ -30987,7 +30986,7 @@
         <v>3203</v>
       </c>
     </row>
-    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>3196</v>
       </c>
@@ -31033,7 +31032,7 @@
         <v>3211</v>
       </c>
     </row>
-    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>3212</v>
       </c>
@@ -31062,7 +31061,7 @@
         <v>44617</v>
       </c>
     </row>
-    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>3219</v>
       </c>
@@ -31091,7 +31090,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>3226</v>
       </c>
@@ -31120,7 +31119,7 @@
         <v>44764</v>
       </c>
     </row>
-    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>3233</v>
       </c>
@@ -31149,7 +31148,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>3240</v>
       </c>
@@ -31178,7 +31177,7 @@
         <v>45133</v>
       </c>
     </row>
-    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>3247</v>
       </c>
@@ -31207,7 +31206,7 @@
         <v>3253</v>
       </c>
     </row>
-    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>3254</v>
       </c>
@@ -31236,7 +31235,7 @@
         <v>3261</v>
       </c>
     </row>
-    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>3262</v>
       </c>
@@ -31265,7 +31264,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>3262</v>
       </c>
@@ -31294,7 +31293,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>3262</v>
       </c>
@@ -31323,7 +31322,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>3262</v>
       </c>
@@ -31352,7 +31351,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>3269</v>
       </c>
@@ -31381,7 +31380,7 @@
         <v>42044</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>3276</v>
       </c>
@@ -31410,7 +31409,7 @@
         <v>45079</v>
       </c>
     </row>
-    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>3283</v>
       </c>
@@ -31439,7 +31438,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>3290</v>
       </c>
@@ -31468,7 +31467,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>3295</v>
       </c>
@@ -31514,7 +31513,7 @@
         <v>45860</v>
       </c>
     </row>
-    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>3303</v>
       </c>
@@ -31543,7 +31542,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>3310</v>
       </c>
@@ -31572,7 +31571,7 @@
         <v>45117</v>
       </c>
     </row>
-    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>3317</v>
       </c>
@@ -31635,7 +31634,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>3332</v>
       </c>
@@ -31664,7 +31663,7 @@
         <v>3339</v>
       </c>
     </row>
-    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>3340</v>
       </c>
@@ -31710,7 +31709,7 @@
         <v>45618</v>
       </c>
     </row>
-    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>3351</v>
       </c>
@@ -31739,7 +31738,7 @@
         <v>45506</v>
       </c>
     </row>
-    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>3358</v>
       </c>
@@ -31785,7 +31784,7 @@
         <v>3369</v>
       </c>
     </row>
-    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>3370</v>
       </c>
@@ -31814,7 +31813,7 @@
         <v>45474</v>
       </c>
     </row>
-    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>3377</v>
       </c>
@@ -31843,7 +31842,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>3377</v>
       </c>
@@ -31872,7 +31871,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>3377</v>
       </c>
@@ -31934,7 +31933,7 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>3391</v>
       </c>
@@ -31963,7 +31962,7 @@
         <v>41499</v>
       </c>
     </row>
-    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>3397</v>
       </c>
@@ -32009,7 +32008,7 @@
         <v>44544</v>
       </c>
     </row>
-    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>3407</v>
       </c>
@@ -32038,7 +32037,7 @@
         <v>3414</v>
       </c>
     </row>
-    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>3415</v>
       </c>
@@ -32067,7 +32066,7 @@
         <v>44508</v>
       </c>
     </row>
-    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>3422</v>
       </c>
@@ -32113,7 +32112,7 @@
         <v>45600</v>
       </c>
     </row>
-    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>3433</v>
       </c>
@@ -32142,7 +32141,7 @@
         <v>42536</v>
       </c>
     </row>
-    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>3440</v>
       </c>
@@ -32171,7 +32170,7 @@
         <v>43837</v>
       </c>
     </row>
-    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>3447</v>
       </c>
@@ -32200,7 +32199,7 @@
         <v>3454</v>
       </c>
     </row>
-    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>3455</v>
       </c>
@@ -32229,7 +32228,7 @@
         <v>43801</v>
       </c>
     </row>
-    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>3462</v>
       </c>
@@ -32258,7 +32257,7 @@
         <v>44747</v>
       </c>
     </row>
-    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>3469</v>
       </c>
@@ -32287,7 +32286,7 @@
         <v>44501</v>
       </c>
     </row>
-    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>3476</v>
       </c>
@@ -32316,7 +32315,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>3481</v>
       </c>
@@ -32345,7 +32344,7 @@
         <v>45133</v>
       </c>
     </row>
-    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>3485</v>
       </c>
@@ -32374,7 +32373,7 @@
         <v>43662</v>
       </c>
     </row>
-    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>3492</v>
       </c>
@@ -32403,7 +32402,7 @@
         <v>45019</v>
       </c>
     </row>
-    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>3496</v>
       </c>
@@ -32432,7 +32431,7 @@
         <v>45484</v>
       </c>
     </row>
-    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>3503</v>
       </c>
@@ -32461,7 +32460,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>3511</v>
       </c>
@@ -32490,7 +32489,7 @@
         <v>44545</v>
       </c>
     </row>
-    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>3515</v>
       </c>
@@ -32536,7 +32535,7 @@
         <v>3526</v>
       </c>
     </row>
-    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>3527</v>
       </c>
@@ -32565,7 +32564,7 @@
         <v>3531</v>
       </c>
     </row>
-    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>3532</v>
       </c>
@@ -32616,7 +32615,7 @@
         <v>3541</v>
       </c>
     </row>
-    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>3542</v>
       </c>
@@ -32642,7 +32641,7 @@
         <v>3547</v>
       </c>
     </row>
-    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>3542</v>
       </c>
@@ -32668,7 +32667,7 @@
         <v>3547</v>
       </c>
     </row>
-    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>3549</v>
       </c>
@@ -32708,7 +32707,7 @@
         <v>3556</v>
       </c>
     </row>
-    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>3557</v>
       </c>
@@ -32737,7 +32736,7 @@
         <v>43878</v>
       </c>
     </row>
-    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>3561</v>
       </c>
@@ -32766,7 +32765,7 @@
         <v>43332</v>
       </c>
     </row>
-    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>3568</v>
       </c>
@@ -32795,7 +32794,7 @@
         <v>3575</v>
       </c>
     </row>
-    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>3576</v>
       </c>
@@ -32824,7 +32823,7 @@
         <v>3583</v>
       </c>
     </row>
-    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>3584</v>
       </c>
@@ -32853,7 +32852,7 @@
         <v>43867</v>
       </c>
     </row>
-    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>3591</v>
       </c>
@@ -32916,7 +32915,7 @@
         <v>45236</v>
       </c>
     </row>
-    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>3606</v>
       </c>
@@ -32996,7 +32995,7 @@
         <v>45281</v>
       </c>
     </row>
-    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>3626</v>
       </c>
@@ -33025,7 +33024,7 @@
         <v>45616</v>
       </c>
     </row>
-    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>3633</v>
       </c>
@@ -33082,7 +33081,7 @@
         <v>3647</v>
       </c>
     </row>
-    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>3648</v>
       </c>
@@ -33111,7 +33110,7 @@
         <v>3652</v>
       </c>
     </row>
-    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>3653</v>
       </c>
@@ -33140,7 +33139,7 @@
         <v>45036</v>
       </c>
     </row>
-    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>3660</v>
       </c>
@@ -33203,7 +33202,7 @@
         <v>44021</v>
       </c>
     </row>
-    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>3675</v>
       </c>
@@ -33232,7 +33231,7 @@
         <v>45177</v>
       </c>
     </row>
-    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>3682</v>
       </c>
@@ -33261,7 +33260,7 @@
         <v>3689</v>
       </c>
     </row>
-    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>3690</v>
       </c>
@@ -33324,7 +33323,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>3705</v>
       </c>
@@ -33353,7 +33352,7 @@
         <v>43119</v>
       </c>
     </row>
-    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>3711</v>
       </c>
@@ -33382,7 +33381,7 @@
         <v>45163</v>
       </c>
     </row>
-    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>3718</v>
       </c>
@@ -33411,7 +33410,7 @@
         <v>44879</v>
       </c>
     </row>
-    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>3725</v>
       </c>
@@ -33440,7 +33439,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>3725</v>
       </c>
@@ -33469,7 +33468,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>3725</v>
       </c>
@@ -33498,7 +33497,7 @@
         <v>45320</v>
       </c>
     </row>
-    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>3725</v>
       </c>
@@ -33555,7 +33554,7 @@
         <v>3735</v>
       </c>
     </row>
-    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>3736</v>
       </c>
@@ -33584,7 +33583,7 @@
         <v>41800</v>
       </c>
     </row>
-    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>3740</v>
       </c>
@@ -33613,7 +33612,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>3740</v>
       </c>
@@ -33642,7 +33641,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>3740</v>
       </c>
@@ -33671,7 +33670,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>3740</v>
       </c>
@@ -33700,7 +33699,7 @@
         <v>44022</v>
       </c>
     </row>
-    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>3750</v>
       </c>
@@ -33751,7 +33750,7 @@
         <v>3762</v>
       </c>
     </row>
-    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>3763</v>
       </c>
@@ -33780,7 +33779,7 @@
         <v>43885</v>
       </c>
     </row>
-    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>3770</v>
       </c>
@@ -33809,7 +33808,7 @@
         <v>43885</v>
       </c>
     </row>
-    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>3777</v>
       </c>
@@ -33838,7 +33837,7 @@
         <v>44970</v>
       </c>
     </row>
-    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>3782</v>
       </c>
@@ -33867,7 +33866,7 @@
         <v>44970</v>
       </c>
     </row>
-    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>3789</v>
       </c>
@@ -33896,7 +33895,7 @@
         <v>44970</v>
       </c>
     </row>
-    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>3791</v>
       </c>
@@ -33942,7 +33941,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>3799</v>
       </c>
@@ -33971,7 +33970,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>3807</v>
       </c>
@@ -34000,7 +33999,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>3807</v>
       </c>
@@ -34029,7 +34028,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>3807</v>
       </c>
@@ -34058,7 +34057,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>3807</v>
       </c>
@@ -34087,7 +34086,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>3814</v>
       </c>
@@ -34116,7 +34115,7 @@
         <v>44585</v>
       </c>
     </row>
-    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>3821</v>
       </c>
@@ -34145,7 +34144,7 @@
         <v>45173</v>
       </c>
     </row>
-    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>3828</v>
       </c>
@@ -34174,7 +34173,7 @@
         <v>43481</v>
       </c>
     </row>
-    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>3835</v>
       </c>
@@ -34203,7 +34202,7 @@
         <v>43788</v>
       </c>
     </row>
-    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>3842</v>
       </c>
@@ -34232,7 +34231,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>3849</v>
       </c>
@@ -34261,7 +34260,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>3849</v>
       </c>
@@ -34290,7 +34289,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>3849</v>
       </c>
@@ -34319,7 +34318,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>3849</v>
       </c>
@@ -34348,7 +34347,7 @@
         <v>44614</v>
       </c>
     </row>
-    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>3858</v>
       </c>
@@ -34394,7 +34393,7 @@
         <v>45169</v>
       </c>
     </row>
-    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>3869</v>
       </c>
@@ -34423,7 +34422,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>3869</v>
       </c>
@@ -34452,7 +34451,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>3869</v>
       </c>
@@ -34481,7 +34480,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>3869</v>
       </c>
@@ -34510,7 +34509,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>3869</v>
       </c>
@@ -34539,7 +34538,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>3869</v>
       </c>
@@ -34568,7 +34567,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>3869</v>
       </c>
@@ -34597,7 +34596,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>3869</v>
       </c>
@@ -34626,7 +34625,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>3869</v>
       </c>
@@ -34655,7 +34654,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>3881</v>
       </c>
@@ -34684,7 +34683,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>3885</v>
       </c>
@@ -34713,7 +34712,7 @@
         <v>45323</v>
       </c>
     </row>
-    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>3889</v>
       </c>
@@ -34742,7 +34741,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>3896</v>
       </c>
@@ -34771,7 +34770,7 @@
         <v>44180</v>
       </c>
     </row>
-    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>3896</v>
       </c>
@@ -34800,7 +34799,7 @@
         <v>44180</v>
       </c>
     </row>
-    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>3896</v>
       </c>
@@ -34829,7 +34828,7 @@
         <v>44180</v>
       </c>
     </row>
-    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>3896</v>
       </c>
@@ -34875,7 +34874,7 @@
         <v>44180</v>
       </c>
     </row>
-    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>3907</v>
       </c>
@@ -34921,7 +34920,7 @@
         <v>3918</v>
       </c>
     </row>
-    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>3919</v>
       </c>
@@ -34950,7 +34949,7 @@
         <v>46030</v>
       </c>
     </row>
-    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>3925</v>
       </c>
@@ -34979,7 +34978,7 @@
         <v>44222</v>
       </c>
     </row>
-    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>3932</v>
       </c>
@@ -35008,7 +35007,7 @@
         <v>43773</v>
       </c>
     </row>
-    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>3939</v>
       </c>
@@ -35037,7 +35036,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>3946</v>
       </c>
@@ -35066,7 +35065,7 @@
         <v>43923</v>
       </c>
     </row>
-    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>3953</v>
       </c>
@@ -35095,7 +35094,7 @@
         <v>43950</v>
       </c>
     </row>
-    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>3960</v>
       </c>
@@ -35124,7 +35123,7 @@
         <v>2758</v>
       </c>
     </row>
-    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>3967</v>
       </c>
@@ -35153,7 +35152,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>3974</v>
       </c>
@@ -35199,7 +35198,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>3986</v>
       </c>
@@ -35228,7 +35227,7 @@
         <v>43049</v>
       </c>
     </row>
-    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>3993</v>
       </c>
@@ -35257,7 +35256,7 @@
         <v>44201</v>
       </c>
     </row>
-    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>4000</v>
       </c>
@@ -35286,7 +35285,7 @@
         <v>4007</v>
       </c>
     </row>
-    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>4008</v>
       </c>
@@ -35315,7 +35314,7 @@
         <v>42710</v>
       </c>
     </row>
-    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>4008</v>
       </c>
@@ -35344,7 +35343,7 @@
         <v>42710</v>
       </c>
     </row>
-    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>4008</v>
       </c>
@@ -35373,7 +35372,7 @@
         <v>42710</v>
       </c>
     </row>
-    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>4008</v>
       </c>
@@ -35402,7 +35401,7 @@
         <v>42710</v>
       </c>
     </row>
-    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>4018</v>
       </c>
@@ -35431,7 +35430,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>4025</v>
       </c>
@@ -35460,7 +35459,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>4029</v>
       </c>
@@ -35489,7 +35488,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>4033</v>
       </c>
@@ -35518,7 +35517,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>4037</v>
       </c>
@@ -35547,7 +35546,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>4041</v>
       </c>
@@ -35576,7 +35575,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>4045</v>
       </c>
@@ -35605,7 +35604,7 @@
         <v>42831</v>
       </c>
     </row>
-    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>4049</v>
       </c>
@@ -35634,7 +35633,7 @@
         <v>44244</v>
       </c>
     </row>
-    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>4053</v>
       </c>
@@ -35663,7 +35662,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>4060</v>
       </c>
@@ -35692,7 +35691,7 @@
         <v>44224</v>
       </c>
     </row>
-    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>4067</v>
       </c>
@@ -35772,7 +35771,7 @@
         <v>4087</v>
       </c>
     </row>
-    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>4088</v>
       </c>
@@ -35801,7 +35800,7 @@
         <v>45103</v>
       </c>
     </row>
-    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>4092</v>
       </c>
@@ -35830,7 +35829,7 @@
         <v>43490</v>
       </c>
     </row>
-    <row r="876" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>4099</v>
       </c>
@@ -35859,7 +35858,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>4099</v>
       </c>
@@ -35888,7 +35887,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="878" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>4099</v>
       </c>
@@ -35917,7 +35916,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="879" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>4099</v>
       </c>
@@ -35946,7 +35945,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="880" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>4109</v>
       </c>
@@ -35992,7 +35991,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>4120</v>
       </c>
@@ -36021,7 +36020,7 @@
         <v>45021</v>
       </c>
     </row>
-    <row r="883" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>4127</v>
       </c>
@@ -36050,7 +36049,7 @@
         <v>43320</v>
       </c>
     </row>
-    <row r="884" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>4134</v>
       </c>
@@ -36113,7 +36112,7 @@
         <v>3613</v>
       </c>
     </row>
-    <row r="887" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>4149</v>
       </c>
@@ -36143,11 +36142,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I887" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I887" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Lesson_development/merged_dataset_ref_with_doi.xlsx
+++ b/Lesson_development/merged_dataset_ref_with_doi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tud365-my.sharepoint.com/personal/linigodelacruz_tudelft_nl/Documents/Documents/4TU.ResearchData/Projects/TRAINING/WebAPI_with_uses_cases/USES-CASES/Sync_Pure_4TU_WUR/Lesson_development/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_76A953B3D350DFA180E81DD04B5ED87656C67458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F846F967-2C4E-41CB-AA27-1F96AA527C55}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_76A953B3D350DFA180E81DD04B5ED87656C67458" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3440FB4-8D25-478E-A681-C48896C9AB52}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12582,10 +12582,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12879,9 +12875,9 @@
     <col min="1" max="1" width="100.140625" customWidth="1"/>
     <col min="2" max="2" width="55.5703125" customWidth="1"/>
     <col min="3" max="3" width="52.5703125" customWidth="1"/>
-    <col min="4" max="4" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="40.85546875" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="67.28515625" customWidth="1"/>
     <col min="7" max="7" width="36.5703125" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
     <col min="9" max="9" width="67" customWidth="1"/>
@@ -36142,7 +36138,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I887" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>